--- a/セリフ編集/キャラタイプ別/蠱惑×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×真面目.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H242"/>
+  <dimension ref="A1:H287"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2988,7 +2988,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.earnest.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.earnest.seductive[1]</t>
+          <t xml:space="preserve">accepted.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3013,14 +3013,14 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかったわ。やれることがあるなら続けるわ</t>
+          <t xml:space="preserve">ここで学んだこと、必ず活かすわ。本当にお世話になりました</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.earnest.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.earnest.seductive[1]</t>
+          <t xml:space="preserve">accepted.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3045,14 +3045,14 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後にもう一度…恥じない闘いをしたいの</t>
+          <t xml:space="preserve">感謝しかないの。新しい場所で、必ず結果を出すから</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">defended.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3077,14 +3077,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかったわ。まだ役に立てるなら全力でやるわ</t>
+          <t xml:space="preserve">…社長の気持ち、伝わったわ。ここで闘い続ける</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.earnest.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.earnest.seductive[1]</t>
+          <t xml:space="preserve">defended.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3109,14 +3109,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じてくれてありがとう。応えてみせるわ</t>
+          <t xml:space="preserve">残らせてもらうわ。必ず恩返しをするから</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.earnest.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.earnest.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3141,14 +3141,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後にいい試合を。それだけが望みよ</t>
+          <t xml:space="preserve">ご恩を返せなくて、ごめんなさい…新天地で必ず結果を出すわ</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3173,14 +3173,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかったわ。最後まで演じきれたなら本望よ</t>
+          <t xml:space="preserve">…ごめんなさい。でも、行かなきゃいけないの</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.earnest.seductive[1]</t>
+          <t xml:space="preserve">default.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3205,14 +3205,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…覚悟はできてたわ。言ってくれてありがとう</t>
+          <t xml:space="preserve">…わかったわ。やれることがあるなら続けるわ</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.earnest.seductive[1]</t>
+          <t xml:space="preserve">former_champ.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3237,14 +3237,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。言ってくれて助かったわ</t>
+          <t xml:space="preserve">最後にもう一度…恥じない闘いをしたいの</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.earnest.seductive[1]</t>
+          <t xml:space="preserve">heel.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3269,14 +3269,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと早く気づくべきだったわ。…わかったわ</t>
+          <t xml:space="preserve">…わかったわ。まだ役に立てるなら全力でやるわ</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.earnest.seductive[1]</t>
+          <t xml:space="preserve">high_trust.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3301,14 +3301,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルトの重み…まだ背負えるわ</t>
+          <t xml:space="preserve">信じてくれてありがとう。応えてみせるわ</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.earnest.seductive[1]</t>
+          <t xml:space="preserve">accept_former_champ.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3333,14 +3333,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体のために尽くしてきたの。嘘じゃないわ</t>
+          <t xml:space="preserve">最後にいい試合を。それだけが望みよ</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.earnest.seductive[1]</t>
+          <t xml:space="preserve">accept_heel.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3365,14 +3365,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだやれることがあるの。止まるわけにはいかないわ</t>
+          <t xml:space="preserve">…わかったわ。最後まで演じきれたなら本望よ</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">accept_no_title.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3397,14 +3397,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の興行で証明するわ。後悔させてみせる</t>
+          <t xml:space="preserve">…覚悟はできてたわ。言ってくれてありがとう</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.earnest.seductive[1]</t>
+          <t xml:space="preserve">accept_terminal.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3429,14 +3429,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルトに恥じない闘い…最後までできたわ</t>
+          <t xml:space="preserve">ありがとう。言ってくれて助かったわ</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.earnest.seductive[1]</t>
+          <t xml:space="preserve">accept_winless.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3461,14 +3461,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夢には届かなかったわ。でも嘘はなかった</t>
+          <t xml:space="preserve">もっと早く気づくべきだったわ。…わかったわ</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">refuse_champ.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3493,14 +3493,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嫌われ役はね…誰かがやらなきゃいけなかったの</t>
+          <t xml:space="preserve">このベルトの重み…まだ背負えるわ</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.earnest.seductive[1]</t>
+          <t xml:space="preserve">refuse_distrust.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3525,14 +3525,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で走り抜けたわ。嘘のない時間だった</t>
+          <t xml:space="preserve">この団体のために尽くしてきたの。嘘じゃないわ</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.earnest.seductive[1]</t>
+          <t xml:space="preserve">refuse_fighting.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3557,14 +3557,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ何も返せてないのに…受け入れられないわ</t>
+          <t xml:space="preserve">まだやれることがあるの。止まるわけにはいかないわ</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.earnest.seductive[1]</t>
+          <t xml:space="preserve">refuse_heel.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3589,14 +3589,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りなかったわ…もっとやりたかった</t>
+          <t xml:space="preserve">次の興行で証明するわ。後悔させてみせる</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.earnest.seductive[1]</t>
+          <t xml:space="preserve">A1_champion.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3621,14 +3621,14 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔いがないとは言わないわ。でも…やりきった</t>
+          <t xml:space="preserve">このベルトに恥じない闘い…最後までできたわ</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.earnest.seductive[1]</t>
+          <t xml:space="preserve">A2_uncrowned.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3653,14 +3653,14 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の防衛戦…やりたかったわ。それだけが心残り</t>
+          <t xml:space="preserve">夢には届かなかったわ。でも嘘はなかった</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3670,12 +3670,12 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">A3_heel.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残るわ。ここで、もっと強くなりたいの</t>
+          <t xml:space="preserve">嫌われ役はね…誰かがやらなきゃいけなかったの</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3702,29 +3702,29 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.earnest.seductive[1]</t>
+          <t xml:space="preserve">A4_veteran.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。…期待に応えるからね。見ててね。</t>
+          <t xml:space="preserve">全力で走り抜けたわ。嘘のない時間だった</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3734,29 +3734,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.earnest.seductive[1]</t>
+          <t xml:space="preserve">B1_young.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、大事な話があるの。{tenure}{record}ちゃんと評価してほしいな</t>
+          <t xml:space="preserve">まだ何も返せてないのに…受け入れられないわ</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3766,641 +3766,641 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.earnest.seductive[1]</t>
+          <t xml:space="preserve">B2_prime.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}ここで過ごした時間は大切よ。でも…次の場所を見つけたいの。</t>
+          <t xml:space="preserve">まだ足りなかったわ…もっとやりたかった</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">B3_older.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">悔いがないとは言わないわ。でも…やりきった</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">B4_champion_injury.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後の防衛戦…やりたかったわ。それだけが心残り</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">残るわ。ここで、もっと強くなりたいの</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_accept.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとう。…期待に応えるからね。見ててね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_negotiate_accept.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……分かったわ。社長の判断だもの、尊重する。この額で、精一杯やるからね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_negotiate_refuse.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……残念ね。でも了解したわ。ただ、この判断のことは覚えておいてね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_open.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、大事な話があるの。{tenure}{record}ちゃんと評価してほしいな</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_refuse.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……承知したわ。でもね、このまま変わらないなら……いずれ考えを改めることになるの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、長い間お世話になったわ。でも、もうここでは続けられないの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">自分なりに、ずっと考えてきたのよ。……ここを去ることにするわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとう。{record}自分なりに考えた結果なの。ここでの経験には感謝してる。でも……新しい場所で挑戦したいのよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}ここで過ごした時間は大切よ。でも…次の場所を見つけたいの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……承知したわ。{tenure_farewell}ここで過ごした日々には、感謝してるの。{rivalry}</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お気持ちは嬉しいの……。でもこの決断は、ずっと考え抜いた末のものよ。ごめんなさい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……社長の誠意、ちゃんと受け取ったわ。もう一度、ここで全力を出すからね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.earnest.seductive[1]</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr" s="2">
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr" s="12">
+      <c r="D124" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.earnest.seductive[1]</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr" s="2">
+      <c r="E124" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr" s="3">
+      <c r="F124" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">今の仲間を途中で捨てるなんて、私には考えられない。
 …ごめんなさい</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="40" customHeight="1">
-      <c r="A110" t="inlineStr" s="15">
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.earnest.seductive[1]</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr" s="2">
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr" s="12">
+      <c r="D125" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.earnest.seductive[1]</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr" s="2">
+      <c r="E125" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr" s="3">
+      <c r="F125" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">みんなを置いて行くわけにはいかないの。
 …ごめんなさい</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="40" customHeight="1">
-      <c r="A111" t="inlineStr" s="15">
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.earnest.seductive[1]</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr" s="2">
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr" s="12">
+      <c r="D126" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.earnest.seductive[1]</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr" s="2">
+      <c r="E126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr" s="3">
+      <c r="F126" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">この団体を離れるのは簡単じゃないの。
 …でも、聞くだけなら</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="40" customHeight="1">
-      <c r="A112" t="inlineStr" s="15">
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.earnest.seductive[1]</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr" s="2">
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr" s="12">
+      <c r="D127" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.earnest.seductive[1]</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr" s="2">
+      <c r="E127" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr" s="3">
+      <c r="F127" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">新しい仲間のために…全力を尽くすわ。
 よろしくね</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="40" customHeight="1">
-      <c r="A113" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちのメンバーのこと、もう少しだけ目を向けてくださいませんか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="40" customHeight="1">
-      <c r="A114" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、次の興行のメイン、私に預けてくれませんか。手応えはあるんです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="40" customHeight="1">
-      <c r="A115" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちの仕事に見合うお手当て、考え直してくださいませんか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="40" customHeight="1">
-      <c r="A116" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私の仕事、届いてるなら一言ください。それで救われる子もいるんです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="40" customHeight="1">
-      <c r="A117" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、ありがとうございます。お言葉、ちゃんと持って帰ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="40" customHeight="1">
-      <c r="A118" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…承知しました。出過ぎた口きいて、すみません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="40" customHeight="1">
-      <c r="A119" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="40" customHeight="1">
-      <c r="A120" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、ありがとうございます。預かった以上、手は抜きません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="40" customHeight="1">
-      <c r="A121" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…承知しました。図々しいことを言いました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="40" customHeight="1">
-      <c r="A122" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…社長、お気遣いありがとうございます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="40" customHeight="1">
-      <c r="A123" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、ありがとうございます。きちんと結果でお返しします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…承知しました。お金の話、出してすみません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、ありがとうございます。お言葉、ちゃんと持って帰ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…承知しました。出過ぎたこと言いました。</t>
-        </is>
-      </c>
-    </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4425,14 +4425,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
+          <t xml:space="preserve">社長、私たちのメンバーのこと、もう少しだけ目を向けてくださいませんか。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4457,14 +4457,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい。輪の外にいる子の気持ち、見えてなかった。</t>
+          <t xml:space="preserve">社長、次の興行のメイン、私に預けてくれませんか。手応えはあるんです。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4489,14 +4489,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。甘え過ぎないようにします。</t>
+          <t xml:space="preserve">社長、私たちの仕事に見合うお手当て、考え直してくださいませんか。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい、配慮が足りませんでした。</t>
+          <t xml:space="preserve">社長、私の仕事、届いてるなら一言ください。それで救われる子もいるんです。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4553,14 +4553,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">社長、ありがとうございます。お言葉、ちゃんと持って帰ります。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4585,14 +4585,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい。リング外まで持ち込んだのは、やりすぎでした。</t>
+          <t xml:space="preserve">…承知しました。出過ぎた口きいて、すみません。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4617,14 +4617,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとうします。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4649,14 +4649,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。立場ある身で、本当に恥ずかしい。</t>
+          <t xml:space="preserve">社長、ありがとうございます。預かった以上、手は抜きません。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4681,14 +4681,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ありがとうございます。次はちゃんとします。</t>
+          <t xml:space="preserve">…承知しました。図々しいことを言いました。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮ありがとうございます。</t>
+          <t xml:space="preserve">…社長、お気遣いありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。ご厚意、頂戴します。</t>
+          <t xml:space="preserve">社長、ありがとうございます。きちんと結果でお返しします。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4777,14 +4777,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご心配ありがとうございます。まだ立てます。</t>
+          <t xml:space="preserve">…承知しました。お金の話、出してすみません。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4809,14 +4809,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。皆に支えてもらえます。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4841,14 +4841,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい。私の目が届いてなかった。</t>
+          <t xml:space="preserve">社長、ありがとうございます。お言葉、ちゃんと持って帰ります。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4873,14 +4873,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ありがとうございます。穏便にいきます。</t>
+          <t xml:space="preserve">…承知しました。出過ぎたこと言いました。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4905,14 +4905,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。下の子も救われます。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4937,14 +4937,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい。わかりやすかったかな。</t>
+          <t xml:space="preserve">…ごめんなさい。輪の外にいる子の気持ち、見えてなかった。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4969,14 +4969,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…静かに目を伏せた）</t>
+          <t xml:space="preserve">…ありがとうございます。甘え過ぎないようにします。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5001,14 +5001,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
+          <t xml:space="preserve">…ごめんなさい、配慮が足りませんでした。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5033,14 +5033,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい。私の判断が行きすぎてました。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5065,14 +5065,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ありがとうございます。責任は私が持ちます。</t>
+          <t xml:space="preserve">…ごめんなさい。リング外まで持ち込んだのは、やりすぎでした。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。私の見落とし、拾ってくれて。</t>
+          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとうします。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.attack.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5129,14 +5129,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">けじめを、つけさせて</t>
+          <t xml:space="preserve">…申し訳ありません。立場ある身で、本当に恥ずかしい。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.defend.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5161,14 +5161,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるつもりはないわ</t>
+          <t xml:space="preserve">…社長、ありがとうございます。次はちゃんとします。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5178,29 +5178,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が実を結んだわ…まだ上を目指すわよ</t>
+          <t xml:space="preserve">…社長、ご配慮ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5210,29 +5210,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきたものが…形になりそうなの</t>
+          <t xml:space="preserve">…ありがとうございます。ご厚意、頂戴します。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5242,29 +5242,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日道場に来るのが…こんなに辛いなんてね</t>
+          <t xml:space="preserve">…ご心配ありがとうございます。まだ立てます。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5274,29 +5274,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">闘う気持ちを忘れてたわ…でもね、もう迷わない</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。皆に支えてもらえます。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5306,29 +5306,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">迷惑かけた分…返すわ、倍にしてね</t>
+          <t xml:space="preserve">…ごめんなさい。私の目が届いてなかった。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.earnest.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5338,29 +5338,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.earnest.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの負けから…ずっと考えてるの、何がいけなかったのかって</t>
+          <t xml:space="preserve">…社長、ありがとうございます。穏便にいきます。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.earnest.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5370,29 +5370,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.earnest.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できたのに…まだ足りないの</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。下の子も救われます。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.earnest.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5402,29 +5402,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.earnest.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できた…でもね、体が覚えてるの、あの痛みを</t>
+          <t xml:space="preserve">…ごめんなさい。わかりやすかったかな。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.earnest.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5434,29 +5434,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.earnest.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治ったわ。でもね、離れていた時間が…重いの</t>
+          <t xml:space="preserve">（…静かに目を伏せた）</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.earnest.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5466,29 +5466,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.earnest.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">準備してきたものを全部出せた。…最高の相手がいたから</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.earnest.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5498,29 +5498,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王者としての誇り、毎試合で証明する。見ていてくれるかしら</t>
+          <t xml:space="preserve">…ごめんなさい。私の判断が行きすぎてました。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.earnest.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5530,29 +5530,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.earnest.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩たちへ。この世界には、努力した人だけが見える景色があるわ。…信じて</t>
+          <t xml:space="preserve">…社長、ありがとうございます。責任は私が持ちます。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.earnest.seductive[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5562,29 +5562,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.earnest.seductive[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきたものが実った。…でも、ここで止まるつもりはないわ</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。私の見落とし、拾ってくれて。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.earnest.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.seductive</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5594,29 +5594,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.earnest.seductive[1]</t>
+          <t xml:space="preserve">earnest.attack.seductive</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力してきたもの。…でもまだ足りないわ。もっと磨くから、見ていて</t>
+          <t xml:space="preserve">けじめを、つけさせて</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.seductive</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5626,29 +5626,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">earnest.defend.seductive</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">真剣勝負よ、今夜は</t>
+          <t xml:space="preserve">逃げるつもりはないわ</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.seductive[2]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5658,29 +5658,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[2]</t>
+          <t xml:space="preserve">earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様の前で…燃えないわけがないでしょう</t>
+          <t xml:space="preserve">練習が実を結んだわ…まだ上を目指すわよ</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.seductive[3]</t>
+          <t xml:space="preserve">BT_HINT_LINES.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[3]</t>
+          <t xml:space="preserve">earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見ていてね、社長</t>
+          <t xml:space="preserve">積み重ねてきたものが…形になりそうなの</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
@@ -5732,19 +5732,19 @@
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の熱気に、私も全力で応えたわ</t>
+          <t xml:space="preserve">毎日道場に来るのが…こんなに辛いなんてね</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.seductive[2]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5754,29 +5754,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[2]</t>
+          <t xml:space="preserve">earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この記録、団体の誇りにしたい</t>
+          <t xml:space="preserve">闘う気持ちを忘れてたわ…でもね、もう迷わない</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.seductive[3]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5786,29 +5786,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[3]</t>
+          <t xml:space="preserve">earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと多くのお客様を、虜にしてみせる</t>
+          <t xml:space="preserve">迷惑かけた分…返すわ、倍にしてね</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.earnest.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5818,29 +5818,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.earnest.seductive[1]</t>
+          <t xml:space="preserve">defeat.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねって大事よね。もっとやりたくなっちゃう</t>
+          <t xml:space="preserve">あの負けから…ずっと考えてるの、何がいけなかったのかって</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.earnest.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5850,29 +5850,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.earnest.seductive[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と一緒だと、もっと頑張りたくなるの</t>
+          <t xml:space="preserve">復帰できたのに…まだ足りないの</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.earnest.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5882,29 +5882,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.earnest.seductive[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…少し休めば、すぐ戻れるわ</t>
+          <t xml:space="preserve">復帰できた…でもね、体が覚えてるの、あの痛みを</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.earnest.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5914,29 +5914,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.earnest.seductive[1]</t>
+          <t xml:space="preserve">penalty_end.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれる人がいるって、本当に力になるの</t>
+          <t xml:space="preserve">怪我は治ったわ。でもね、離れていた時間が…重いの</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.earnest.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5946,29 +5946,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.earnest.seductive[1]</t>
+          <t xml:space="preserve">bestMatch.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切りたいわけじゃないの。ただ……ね</t>
+          <t xml:space="preserve">準備してきたものを全部出せた。…最高の相手がいたから</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.earnest.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5978,29 +5978,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.earnest.seductive[1]</t>
+          <t xml:space="preserve">champion.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いくら練習しても、何か足りない気がして…</t>
+          <t xml:space="preserve">王者としての誇り、毎試合で証明する。見ていてくれるかしら</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.earnest.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6010,29 +6010,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.earnest.seductive[1]</t>
+          <t xml:space="preserve">hallOfFame.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。ちゃんと結果で返すわ</t>
+          <t xml:space="preserve">後輩たちへ。この世界には、努力した人だけが見える景色があるわ。…信じて</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.earnest.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6042,29 +6042,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.earnest.seductive[1]</t>
+          <t xml:space="preserve">mvp.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">思い切り鍛えられるのね。楽しみだわ</t>
+          <t xml:space="preserve">積み重ねてきたものが実った。…でも、ここで止まるつもりはないわ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.earnest.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6074,29 +6074,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.earnest.seductive[1]</t>
+          <t xml:space="preserve">rookie.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見てくれてたのね…絶対に報いるわ</t>
+          <t xml:space="preserve">努力してきたもの。…でもまだ足りないわ。もっと磨くから、見ていて</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.earnest.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6106,29 +6106,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.earnest.seductive[1]</t>
+          <t xml:space="preserve">earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう…もう一度、頑張ってみるわ</t>
+          <t xml:space="preserve">真剣勝負よ、今夜は</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.earnest.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6138,29 +6138,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.earnest.seductive[1]</t>
+          <t xml:space="preserve">earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張するけど…精一杯やるわ</t>
+          <t xml:space="preserve">満員のお客様の前で…燃えないわけがないでしょう</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.earnest.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.seductive[3]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6170,29 +6170,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.earnest.seductive[1]</t>
+          <t xml:space="preserve">earnest.seductive[3]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お疲れ様。また明日から頑張りましょうね</t>
+          <t xml:space="preserve">…見ていてね、社長</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.earnest.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6202,29 +6202,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.earnest.seductive[1]</t>
+          <t xml:space="preserve">earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が気になるけど…ありがとう。休んでくるわ</t>
+          <t xml:space="preserve">お客様の熱気に、私も全力で応えたわ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.earnest.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6234,29 +6234,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.earnest.seductive[1]</t>
+          <t xml:space="preserve">earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな機会をもらえるなんて…全力で応えるわ</t>
+          <t xml:space="preserve">この記録、団体の誇りにしたい</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.earnest.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.seductive[3]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6266,29 +6266,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.earnest.seductive[1]</t>
+          <t xml:space="preserve">earnest.seductive[3]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張するけど…精一杯やるわ</t>
+          <t xml:space="preserve">次はもっと多くのお客様を、虜にしてみせる</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.earnest.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6298,29 +6298,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.earnest.seductive[1]</t>
+          <t xml:space="preserve">N1.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">義理があるから断ったけど…報告はしておくわね</t>
+          <t xml:space="preserve">積み重ねって大事よね。もっとやりたくなっちゃう</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.earnest.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6330,29 +6330,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.earnest.seductive[1]</t>
+          <t xml:space="preserve">N2.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと準備してきたの。チャンスをちょうだい</t>
+          <t xml:space="preserve">あの人と一緒だと、もっと頑張りたくなるの</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.earnest.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6362,29 +6362,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.earnest.seductive[1]</t>
+          <t xml:space="preserve">N3.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人を越えたいの。試合を組んでくれない？</t>
+          <t xml:space="preserve">ごめんなさい…少し休めば、すぐ戻れるわ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.earnest.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6394,29 +6394,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.earnest.seductive[1]</t>
+          <t xml:space="preserve">N4.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">迷惑かけたくないんだけど…体が限界なの…</t>
+          <t xml:space="preserve">応援してくれる人がいるって、本当に力になるの</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.earnest.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6426,29 +6426,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.earnest.seductive[1]</t>
+          <t xml:space="preserve">N5_low.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと我慢してきたの。でも、もう限界よ</t>
+          <t xml:space="preserve">裏切りたいわけじゃないの。ただ……ね</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.earnest.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6458,29 +6458,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.earnest.seductive[1]</t>
+          <t xml:space="preserve">N5_warning.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいの。特訓させてもらえる？</t>
+          <t xml:space="preserve">いくら練習しても、何か足りない気がして…</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.earnest.seductive[1]</t>
+          <t xml:space="preserve">bonus.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6505,14 +6505,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">培ってきたものを、次の子たちに伝えたいの</t>
+          <t xml:space="preserve">ありがとう。ちゃんと結果で返すわ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.earnest.seductive[1]</t>
+          <t xml:space="preserve">camp.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6537,14 +6537,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…早く戻れるように頑張るわ</t>
+          <t xml:space="preserve">思い切り鍛えられるのね。楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6554,12 +6554,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.earnest.seductive[1]</t>
+          <t xml:space="preserve">encourage_high_trust.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6569,14 +6569,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と一緒じゃ仕事にならないの。何とかして</t>
+          <t xml:space="preserve">ずっと見てくれてたのね…絶対に報いるわ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.earnest.seductive[1]</t>
+          <t xml:space="preserve">encourage.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6601,14 +6601,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">迷惑はかけたくないけど…あの人とはもう無理なの</t>
+          <t xml:space="preserve">ありがとう…もう一度、頑張ってみるわ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.earnest.seductive[1]</t>
+          <t xml:space="preserve">media.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6633,14 +6633,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちゃんとブランドのイメージに合わせて取り組むわ</t>
+          <t xml:space="preserve">緊張するけど…精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6650,12 +6650,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.earnest.seductive[1]</t>
+          <t xml:space="preserve">party.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6665,14 +6665,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちゃんと準備して、いい姿を見せるわ</t>
+          <t xml:space="preserve">お疲れ様。また明日から頑張りましょうね</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.earnest.seductive[1]</t>
+          <t xml:space="preserve">refresh_leave.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6697,14 +6697,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ひとりにちゃんと向き合う。それが大事だと思うわ</t>
+          <t xml:space="preserve">練習が気になるけど…ありがとう。休んでくるわ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.earnest.seductive[1]</t>
+          <t xml:space="preserve">special_treatment.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6729,14 +6729,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">きちんと練習して、完璧に歩いてみせるわ</t>
+          <t xml:space="preserve">ありがとう…早く戻れるように頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.earnest.seductive[1]</t>
+          <t xml:space="preserve">trainer.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6761,14 +6761,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">きちんと準備して、いい仕上がりにするわ</t>
+          <t xml:space="preserve">こんな機会をもらえるなんて…全力で応えるわ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.earnest.seductive[1]</t>
+          <t xml:space="preserve">E1.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6793,14 +6793,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちゃんと準備して、面白い話ができるよう頑張るわ</t>
+          <t xml:space="preserve">緊張するけど…精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.earnest.seductive[1]</t>
+          <t xml:space="preserve">E6.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6825,14 +6825,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私でいいの？ …精一杯頑張るわ</t>
+          <t xml:space="preserve">義理があるから断ったけど…報告はしておくわね</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6842,29 +6842,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">S_boycott.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道に頑張るタイプよ。見ていてくれる？</t>
+          <t xml:space="preserve">ごめんなさい…今日はどうしても、体が動かなくて…</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6874,29 +6874,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">S_boycott.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれてありがとう。期待に応えるわ</t>
+          <t xml:space="preserve">練習に集中できないの…ごめんなさいね…</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6906,29 +6906,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">S_grumble.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。期待に応えるわ</t>
+          <t xml:space="preserve">（「わたし、このままでいいのかしら」と後輩に弱音を漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6938,29 +6938,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">S_sns.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日頑張るわ。見ていてね</t>
+          <t xml:space="preserve">（SNSに「わたし、ここで必要とされているのかしら」と率直な投稿）</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6970,29 +6970,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">S1.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれてる人に申し訳ないわ…必ず戻る</t>
+          <t xml:space="preserve">ずっと準備してきたの。チャンスをちょうだい</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7002,29 +7002,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.earnest.seductive[1]</t>
+          <t xml:space="preserve">S2.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道に頑張るタイプよ。見ていてくれる？</t>
+          <t xml:space="preserve">あの人を越えたいの。試合を組んでくれない？</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7034,29 +7034,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.earnest.seductive[1]</t>
+          <t xml:space="preserve">S3.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれてありがとう。期待に応えるわ</t>
+          <t xml:space="preserve">迷惑かけたくないんだけど…体が限界なの…</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7066,29 +7066,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.earnest.seductive[1]</t>
+          <t xml:space="preserve">S4_direct.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。期待に応えるわ</t>
+          <t xml:space="preserve">ずっと我慢してきたの。でも、もう限界よ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7098,29 +7098,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.earnest.seductive[1]</t>
+          <t xml:space="preserve">S4_silent.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日頑張るわ。見ていてね</t>
+          <t xml:space="preserve">…………（言いかけた言葉を、笑みの奥に飲み込んだ）</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7130,29 +7130,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.earnest.seductive[1]</t>
+          <t xml:space="preserve">S5.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれてる人に申し訳ないわ…必ず戻る</t>
+          <t xml:space="preserve">もっと強くなりたいの。特訓させてもらえる？</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7162,29 +7162,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.earnest.seductive[1]</t>
+          <t xml:space="preserve">S6.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれた人たちに、申し訳ないわ…必ず見返す</t>
+          <t xml:space="preserve">培ってきたものを、次の子たちに伝えたいの</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7194,29 +7194,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.earnest.seductive[1]</t>
+          <t xml:space="preserve">B1.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間だけど、精一杯やるわ</t>
+          <t xml:space="preserve">ごめんなさい…早く戻れるように頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7226,29 +7226,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.earnest.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter1.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかったわ…でも、もう一度挑戦する</t>
+          <t xml:space="preserve">あの人と一緒じゃ仕事にならないの。何とかして</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7258,29 +7258,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.earnest.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter2.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できたわ…でも満足しない。もっと強くなる</t>
+          <t xml:space="preserve">迷惑はかけたくないけど…あの人とはもう無理なの</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7290,29 +7290,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.earnest.seductive[1]</t>
+          <t xml:space="preserve">B4_brand.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった…でも、ここで終わりにはしないわ</t>
+          <t xml:space="preserve">ちゃんとブランドのイメージに合わせて取り組むわ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7322,29 +7322,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.earnest.seductive[1]</t>
+          <t xml:space="preserve">B4_cm.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきて…よかった。このベルト、大切にするわ</t>
+          <t xml:space="preserve">ちゃんと準備して、いい姿を見せるわ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7354,29 +7354,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">B4_fan.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれた人たちに、申し訳ないわ…必ず見返す</t>
+          <t xml:space="preserve">一人ひとりにちゃんと向き合う。それが大事だと思うわ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7386,29 +7386,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">B4_fashion.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間だけど、精一杯やるわ</t>
+          <t xml:space="preserve">きちんと練習して、完璧に歩いてみせるわ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7418,29 +7418,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">B4_gravure.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかったわ…でも、もう一度挑戦する</t>
+          <t xml:space="preserve">きちんと準備して、いい仕上がりにするわ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7450,29 +7450,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">B4_variety.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できたわ…でも満足しない。もっと強くなる</t>
+          <t xml:space="preserve">ちゃんと準備して、面白い話ができるよう頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7482,29 +7482,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">B4.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった…でも、ここで終わりにはしないわ</t>
+          <t xml:space="preserve">私でいいの？ …精一杯頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
@@ -7529,14 +7529,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきて…よかった。このベルト、大切にするわ</t>
+          <t xml:space="preserve">地道に頑張るタイプよ。見ていてくれる？</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7546,29 +7546,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒のトレーニング、刺激があっていいわ</t>
+          <t xml:space="preserve">選んでくれてありがとう。期待に応えるわ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7578,29 +7578,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.seductive[1]</t>
+          <t xml:space="preserve">earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">繋いでもらったこの舞台、崩す気はないの。傷ごと、立つわ</t>
+          <t xml:space="preserve">ありがとう。期待に応えるわ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.seductive[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7610,29 +7610,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.seductive[2]</t>
+          <t xml:space="preserve">earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来た以上、最後まできっちり向き合うわ。それが筋でしょ</t>
+          <t xml:space="preserve">毎日頑張るわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7642,29 +7642,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.seductive[1]</t>
+          <t xml:space="preserve">earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手が誰でも、ちゃんと向き合うわ。手を抜くなんて、できないの</t>
+          <t xml:space="preserve">応援してくれてる人に申し訳ないわ…必ず戻る</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7674,29 +7674,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.seductive[2]</t>
+          <t xml:space="preserve">draftInterest.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">繋ぐ相手がいる。だから、この一戦も手は抜けないの</t>
+          <t xml:space="preserve">地道に頑張るタイプよ。見ていてくれる？</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7706,29 +7706,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.seductive[1]</t>
+          <t xml:space="preserve">draftJoin.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒したわ。…でも、まだ役目の途中なの。次、出してよ。ちゃんと相手するから</t>
+          <t xml:space="preserve">選んでくれてありがとう。期待に応えるわ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7738,29 +7738,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.seductive[2]</t>
+          <t xml:space="preserve">faGreeting.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの。繋ぐまでは、退けない。次の子、来なさい</t>
+          <t xml:space="preserve">声をかけてくれた人は久しぶりなの。…このチャンス、大事にするわ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7770,29 +7770,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.seductive[1]</t>
+          <t xml:space="preserve">faSigning.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で紡いだ勝利よ。この結び目を、一人でほどく気はないわ</t>
+          <t xml:space="preserve">ありがとう。期待に応えるわ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7802,29 +7802,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.seductive[2]</t>
+          <t xml:space="preserve">faWelcome.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が信じてくれた……その信頼に、ちゃんと応えられたかしら</t>
+          <t xml:space="preserve">毎日頑張るわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7834,29 +7834,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.seductive[1]</t>
+          <t xml:space="preserve">injury.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞は嬉しいわ。でも……本当に欲しかったのは、三人で掴む勝利</t>
+          <t xml:space="preserve">応援してくれてる人に申し訳ないわ…必ず戻る</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7866,29 +7866,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.seductive[2]</t>
+          <t xml:space="preserve">release.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった分は、次に全て返す。約束するわ</t>
+          <t xml:space="preserve">応援してくれた人たちに、申し訳ないわ…必ず見返す</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7898,29 +7898,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.seductive[1]</t>
+          <t xml:space="preserve">rentalGreeting.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人一人、ちゃんと向き合ったわ。この身体で返した答えよ</t>
+          <t xml:space="preserve">短い間だけど、精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.seductive[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7930,29 +7930,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.seductive[2]</t>
+          <t xml:space="preserve">scoutGreeting.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界なんて何度も見えた。でも……ここで崩れるのは、許せなかったの</t>
+          <t xml:space="preserve">評価してくれたのね。…ちゃんと応えるわ</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7962,29 +7962,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でいくわ。最高の試合にしましょう</t>
+          <t xml:space="preserve">足りなかったわ…でも、もう一度挑戦する</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7994,29 +7994,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">titleDefense.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られたのは、支えてくれた皆のおかげよ。…ありがとう</t>
+          <t xml:space="preserve">防衛できたわ…でも満足しない。もっと強くなる</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8026,59 +8026,1499 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">titleLoss.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体のために戦えて…嬉しいわ</t>
+          <t xml:space="preserve">足りなかった…でも、ここで終わりにはしないわ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleWin.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">積み重ねてきて…よかった。このベルト、大切にするわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">応援してくれた人たちに、申し訳ないわ…必ず見返す</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">短い間だけど、精一杯やるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">足りなかったわ…でも、もう一度挑戦する</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">防衛できたわ…でも満足しない。もっと強くなる</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">足りなかった…でも、ここで終わりにはしないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">積み重ねてきて…よかった。このベルト、大切にするわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この関係…直せる自信がないの…</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">どこで間違えたのかしら…</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この距離…私の何がいけなかったのかしら</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう一度分かり合えるよう、努力しないとね</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_60_up.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一緒のトレーニング、刺激があっていいわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一緒に頂点まで行きたいの。二人ならきっと届くわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高の相棒ね。この出会いに感謝してる</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="40" customHeight="1">
+      <c r="A256" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">関係も変わったわね。前に進みましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="40" customHeight="1">
+      <c r="A257" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの因縁から学んだことは多いの。次の目標を見つけなきゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="40" customHeight="1">
+      <c r="A258" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">好敵手として意識し始めてるみたい</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="40" customHeight="1">
+      <c r="A259" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">超えることが、今の一番の目標なの</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="40" customHeight="1">
+      <c r="A260" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この壁を越えない限り、私に先はないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="40" customHeight="1">
+      <c r="A261" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最大の壁。だからこそ、越えなきゃいけないの</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="40" customHeight="1">
+      <c r="A262" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの存在が私を高めてくれる。これが宿命というものかしら</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="40" customHeight="1">
+      <c r="A263" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">戦えることに感謝してる。でも次は絶対に勝つわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="40" customHeight="1">
+      <c r="A264" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この団体に貢献できるよう、これからも全力で努めるわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="40" customHeight="1">
+      <c r="A265" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここでプロレスができる幸せを噛みしめてるの</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="40" customHeight="1">
+      <c r="A266" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">信じてたのに…もうここでは頑張れないかもしれないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力を尽くしてきたつもりよ。でも、もう…</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この団体の方針に…少し不安を感じてるの</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="40" customHeight="1">
+      <c r="A269" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">自分の居場所がここにあるのか…考えてしまうわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">繋いでもらったこの舞台、崩す気はないの。傷ごと、立つわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来た以上、最後まできっちり向き合うわ。それが筋でしょ</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">相手が誰でも、ちゃんと向き合うわ。手を抜くなんて、できないの</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">繋ぐ相手がいる。だから、この一戦も手は抜けないの</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="40" customHeight="1">
+      <c r="A274" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人、倒したわ。…でも、まだ役目の途中なの。次、出してよ。ちゃんと相手するから</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="40" customHeight="1">
+      <c r="A275" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ立ってるの。繋ぐまでは、退けない。次の子、来なさい</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="40" customHeight="1">
+      <c r="A276" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">三人で紡いだ勝利よ。この結び目を、一人でほどく気はないわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="40" customHeight="1">
+      <c r="A277" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仲間が信じてくれた……その信頼に、ちゃんと応えられたかしら</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="40" customHeight="1">
+      <c r="A278" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">賞は嬉しいわ。でも……本当に欲しかったのは、三人で掴む勝利</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="40" customHeight="1">
+      <c r="A279" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">足りなかった分は、次に全て返す。約束するわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="40" customHeight="1">
+      <c r="A280" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人一人、ちゃんと向き合ったわ。この身体で返した答えよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.earnest.seductive[2]</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">限界なんて何度も見えた。でも……ここで崩れるのは、許せなかったの</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力でいくわ。最高の試合にしましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来られたのは、支えてくれた皆のおかげよ。…ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体のために戦えて…嬉しいわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.earnest.seductive[1]</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr" s="2">
+      <c r="B285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr" s="12">
+      <c r="D285" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.earnest.seductive[1]</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr" s="2">
+      <c r="E285" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr" s="3">
+      <c r="F285" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">積み重ねてきた全部が報われた…泣きそうだわ</t>
         </is>
       </c>
     </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてくれた人は久しぶりなの。…このチャンス、大事にするわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">earnest.seductive[1]</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">評価してくれたのね。…ちゃんと応えるわ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H242"/>
+  <autoFilter ref="A1:H287"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×真面目.xlsx
@@ -364,7 +364,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -379,7 +379,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.seductive[1]</t>
+          <t xml:space="preserve">atk.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -396,7 +396,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -411,7 +411,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.seductive[2]</t>
+          <t xml:space="preserve">atk.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -428,7 +428,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.earnest[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -443,7 +443,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.seductive[3]</t>
+          <t xml:space="preserve">atk.seductive.earnest[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -460,7 +460,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.earnest.seductive[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.seductive.earnest[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -475,7 +475,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.earnest.seductive[4]</t>
+          <t xml:space="preserve">atk.seductive.earnest[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -492,7 +492,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -507,7 +507,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.earnest.seductive[1]</t>
+          <t xml:space="preserve">bigmove.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -524,7 +524,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -539,7 +539,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.earnest.seductive[2]</t>
+          <t xml:space="preserve">bigmove.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -556,7 +556,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.earnest.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.seductive.earnest[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -571,7 +571,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.earnest.seductive[3]</t>
+          <t xml:space="preserve">bigmove.seductive.earnest[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -588,7 +588,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.earnest.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -603,7 +603,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.earnest.seductive[1]</t>
+          <t xml:space="preserve">climax.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -620,7 +620,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.earnest.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -635,7 +635,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.earnest.seductive[2]</t>
+          <t xml:space="preserve">climax.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -652,7 +652,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -667,7 +667,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -684,7 +684,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.earnest.seductive[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -699,7 +699,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[2]</t>
+          <t xml:space="preserve">seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -716,7 +716,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.earnest.seductive[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.seductive.earnest[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -731,7 +731,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[3]</t>
+          <t xml:space="preserve">seductive.earnest[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -748,7 +748,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.earnest.seductive[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -763,7 +763,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.earnest.seductive[1]</t>
+          <t xml:space="preserve">badWinner.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -780,7 +780,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.earnest.seductive[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -795,7 +795,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.earnest.seductive[1]</t>
+          <t xml:space="preserve">goodWinner.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -812,7 +812,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.earnest.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -827,7 +827,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.earnest.seductive[1]</t>
+          <t xml:space="preserve">competition_won.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -844,7 +844,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.earnest.seductive[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -859,7 +859,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.earnest.seductive[2]</t>
+          <t xml:space="preserve">competition_won.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -876,7 +876,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.earnest.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -891,7 +891,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.earnest.seductive[1]</t>
+          <t xml:space="preserve">direct.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -908,7 +908,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.earnest.seductive[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -923,7 +923,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.earnest.seductive[2]</t>
+          <t xml:space="preserve">direct.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -940,7 +940,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.earnest.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -955,7 +955,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.earnest.seductive[1]</t>
+          <t xml:space="preserve">fa_signing.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -972,7 +972,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.earnest.seductive[2]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -987,7 +987,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.earnest.seductive[2]</t>
+          <t xml:space="preserve">fa_signing.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1004,7 +1004,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.seductive.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.earnest.hit[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive.hit[1]</t>
+          <t xml:space="preserve">seductive.earnest.hit[1]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1036,7 +1036,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.seductive.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.earnest.hit[2]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive.hit[2]</t>
+          <t xml:space="preserve">seductive.earnest.hit[2]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1068,7 +1068,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.seductive.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.earnest.win[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive.win[1]</t>
+          <t xml:space="preserve">seductive.earnest.win[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1100,7 +1100,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.earnest.seductive.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.seductive.earnest.win[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive.win[2]</t>
+          <t xml:space="preserve">seductive.earnest.win[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1132,7 +1132,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1164,7 +1164,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.earnest.seductive[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[2]</t>
+          <t xml:space="preserve">seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1196,7 +1196,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.earnest.seductive[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.seductive.earnest[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[3]</t>
+          <t xml:space="preserve">seductive.earnest[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1228,7 +1228,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1260,7 +1260,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.earnest.seductive[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[2]</t>
+          <t xml:space="preserve">seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1292,7 +1292,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.earnest.seductive[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.seductive.earnest[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[3]</t>
+          <t xml:space="preserve">seductive.earnest[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1324,7 +1324,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1356,7 +1356,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.earnest.seductive[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[2]</t>
+          <t xml:space="preserve">seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1388,7 +1388,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.earnest.seductive[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.seductive.earnest[3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[3]</t>
+          <t xml:space="preserve">seductive.earnest[3]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1420,7 +1420,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1452,7 +1452,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.earnest.seductive[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[2]</t>
+          <t xml:space="preserve">seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1484,7 +1484,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.earnest.seductive[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.seductive.earnest[3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[3]</t>
+          <t xml:space="preserve">seductive.earnest[3]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1516,7 +1516,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1548,7 +1548,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.earnest.seductive[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[2]</t>
+          <t xml:space="preserve">seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1580,7 +1580,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1612,7 +1612,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.earnest.seductive[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[2]</t>
+          <t xml:space="preserve">seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1644,7 +1644,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.earnest.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1676,7 +1676,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.earnest.seductive[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1708,7 +1708,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.earnest.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1740,7 +1740,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.earnest.seductive[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1772,7 +1772,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.earnest.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1804,7 +1804,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.earnest.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1836,7 +1836,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.earnest.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1868,7 +1868,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.earnest.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1900,7 +1900,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.earnest.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.earnest.seductive[1]</t>
+          <t xml:space="preserve">attacker.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1932,7 +1932,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.earnest.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.earnest.seductive[1]</t>
+          <t xml:space="preserve">defender.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1964,7 +1964,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.earnest.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.earnest.seductive[1]</t>
+          <t xml:space="preserve">fateAttacker.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1996,7 +1996,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.earnest.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.earnest.seductive[1]</t>
+          <t xml:space="preserve">fateDefender.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2028,7 +2028,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.earnest.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest.seductive[1]</t>
+          <t xml:space="preserve">loserLines.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2060,7 +2060,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.earnest.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest.seductive[1]</t>
+          <t xml:space="preserve">winnerLines.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2092,7 +2092,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.earnest.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.earnest.seductive[1]</t>
+          <t xml:space="preserve">loser.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2124,7 +2124,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.earnest.seductive[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.earnest.seductive[1]</t>
+          <t xml:space="preserve">winner.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2156,7 +2156,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.earnest.seductive[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.earnest.seductive[1]</t>
+          <t xml:space="preserve">loserLines.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2188,7 +2188,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.earnest.seductive[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.earnest.seductive[1]</t>
+          <t xml:space="preserve">winnerLines.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2988,7 +2988,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.earnest.seductive[1]</t>
+          <t xml:space="preserve">accepted.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3020,7 +3020,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest.seductive[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.earnest.seductive[2]</t>
+          <t xml:space="preserve">accepted.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3052,7 +3052,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.earnest.seductive[1]</t>
+          <t xml:space="preserve">defended.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3084,7 +3084,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest.seductive[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.earnest.seductive[2]</t>
+          <t xml:space="preserve">defended.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3116,7 +3116,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest.seductive[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.earnest.seductive[1]</t>
+          <t xml:space="preserve">defense_failed.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3148,7 +3148,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest.seductive[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.earnest.seductive[2]</t>
+          <t xml:space="preserve">defense_failed.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3180,7 +3180,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.earnest.seductive[1]</t>
+          <t xml:space="preserve">default.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3212,7 +3212,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.earnest.seductive[1]</t>
+          <t xml:space="preserve">former_champ.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3244,7 +3244,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">heel.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3276,7 +3276,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.earnest.seductive[1]</t>
+          <t xml:space="preserve">high_trust.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3308,7 +3308,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.earnest.seductive[1]</t>
+          <t xml:space="preserve">accept_former_champ.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3340,7 +3340,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">accept_heel.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3372,7 +3372,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.earnest.seductive[1]</t>
+          <t xml:space="preserve">accept_no_title.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3404,7 +3404,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.earnest.seductive[1]</t>
+          <t xml:space="preserve">accept_terminal.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3436,7 +3436,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.earnest.seductive[1]</t>
+          <t xml:space="preserve">accept_winless.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3468,7 +3468,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.earnest.seductive[1]</t>
+          <t xml:space="preserve">refuse_champ.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3500,7 +3500,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.earnest.seductive[1]</t>
+          <t xml:space="preserve">refuse_distrust.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3532,7 +3532,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.earnest.seductive[1]</t>
+          <t xml:space="preserve">refuse_fighting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3564,7 +3564,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">refuse_heel.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3596,7 +3596,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.earnest.seductive[1]</t>
+          <t xml:space="preserve">A1_champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3628,7 +3628,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.earnest.seductive[1]</t>
+          <t xml:space="preserve">A2_uncrowned.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3660,7 +3660,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.earnest.seductive[1]</t>
+          <t xml:space="preserve">A3_heel.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3692,7 +3692,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.earnest.seductive[1]</t>
+          <t xml:space="preserve">A4_veteran.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3724,7 +3724,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.earnest.seductive[1]</t>
+          <t xml:space="preserve">B1_young.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3756,7 +3756,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.earnest.seductive[1]</t>
+          <t xml:space="preserve">B2_prime.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3788,7 +3788,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.earnest.seductive[1]</t>
+          <t xml:space="preserve">B3_older.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3820,7 +3820,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.earnest.seductive[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.earnest.seductive[1]</t>
+          <t xml:space="preserve">B4_champion_injury.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3852,7 +3852,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3884,7 +3884,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.earnest.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.earnest.seductive[1]</t>
+          <t xml:space="preserve">raise_accept.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3916,7 +3916,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.earnest.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.earnest.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3948,7 +3948,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.earnest.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.earnest.seductive[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3980,7 +3980,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.earnest.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.earnest.seductive[1]</t>
+          <t xml:space="preserve">raise_open.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4012,7 +4012,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.earnest.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.earnest.seductive[1]</t>
+          <t xml:space="preserve">raise_refuse.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4044,7 +4044,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest.seductive[1]</t>
+          <t xml:space="preserve">sudden_departure.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4076,7 +4076,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.earnest.seductive[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.earnest.seductive[2]</t>
+          <t xml:space="preserve">sudden_departure.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4108,7 +4108,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.earnest.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.earnest.seductive[1]</t>
+          <t xml:space="preserve">transfer_listen.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4140,7 +4140,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.earnest.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.earnest.seductive[1]</t>
+          <t xml:space="preserve">transfer_open.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4172,7 +4172,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.earnest.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.earnest.seductive[1]</t>
+          <t xml:space="preserve">transfer_release.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4204,7 +4204,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.earnest.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.earnest.seductive[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4236,7 +4236,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.earnest.seductive[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.earnest.seductive[1]</t>
+          <t xml:space="preserve">transfer_retain_success.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4268,7 +4268,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.earnest.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.earnest.seductive[1]</t>
+          <t xml:space="preserve">blocked.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4301,7 +4301,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.earnest.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.earnest.seductive[1]</t>
+          <t xml:space="preserve">fail.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4334,7 +4334,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.earnest.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.earnest.seductive[1]</t>
+          <t xml:space="preserve">start.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4367,7 +4367,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.earnest.seductive[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.earnest.seductive[1]</t>
+          <t xml:space="preserve">success.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -5648,7 +5648,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5680,7 +5680,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5712,7 +5712,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5744,7 +5744,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5776,7 +5776,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5808,7 +5808,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.earnest.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.earnest.seductive[1]</t>
+          <t xml:space="preserve">defeat.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5840,7 +5840,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.earnest.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.earnest.seductive[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5872,7 +5872,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.earnest.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.earnest.seductive[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5904,7 +5904,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.earnest.seductive[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.earnest.seductive[1]</t>
+          <t xml:space="preserve">penalty_end.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5936,7 +5936,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.earnest.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.earnest.seductive[1]</t>
+          <t xml:space="preserve">bestMatch.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5968,7 +5968,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.earnest.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.seductive[1]</t>
+          <t xml:space="preserve">champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6000,7 +6000,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.earnest.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.earnest.seductive[1]</t>
+          <t xml:space="preserve">hallOfFame.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6032,7 +6032,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.earnest.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.earnest.seductive[1]</t>
+          <t xml:space="preserve">mvp.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6064,7 +6064,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.earnest.seductive[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.earnest.seductive[1]</t>
+          <t xml:space="preserve">rookie.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6096,7 +6096,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6128,7 +6128,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.seductive[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[2]</t>
+          <t xml:space="preserve">seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6160,7 +6160,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.earnest.seductive[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.earnest[3]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[3]</t>
+          <t xml:space="preserve">seductive.earnest[3]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6192,7 +6192,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6224,7 +6224,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.seductive[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[2]</t>
+          <t xml:space="preserve">seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6256,7 +6256,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.earnest.seductive[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.earnest[3]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[3]</t>
+          <t xml:space="preserve">seductive.earnest[3]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6288,7 +6288,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.earnest.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.earnest.seductive[1]</t>
+          <t xml:space="preserve">N1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6320,7 +6320,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.earnest.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.earnest.seductive[1]</t>
+          <t xml:space="preserve">N2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6352,7 +6352,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.earnest.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.earnest.seductive[1]</t>
+          <t xml:space="preserve">N3.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6384,7 +6384,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.earnest.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.earnest.seductive[1]</t>
+          <t xml:space="preserve">N4.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6416,7 +6416,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.earnest.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.earnest.seductive[1]</t>
+          <t xml:space="preserve">N5_low.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6448,7 +6448,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.earnest.seductive[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.earnest.seductive[1]</t>
+          <t xml:space="preserve">N5_warning.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6480,7 +6480,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.earnest.seductive[1]</t>
+          <t xml:space="preserve">bonus.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6512,7 +6512,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.earnest.seductive[1]</t>
+          <t xml:space="preserve">camp.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6544,7 +6544,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.earnest.seductive[1]</t>
+          <t xml:space="preserve">encourage_high_trust.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6576,7 +6576,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.earnest.seductive[1]</t>
+          <t xml:space="preserve">encourage.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6608,7 +6608,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.earnest.seductive[1]</t>
+          <t xml:space="preserve">media.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6640,7 +6640,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.earnest.seductive[1]</t>
+          <t xml:space="preserve">party.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6672,7 +6672,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.earnest.seductive[1]</t>
+          <t xml:space="preserve">refresh_leave.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6704,7 +6704,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.earnest.seductive[1]</t>
+          <t xml:space="preserve">special_treatment.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6736,7 +6736,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.earnest.seductive[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.earnest.seductive[1]</t>
+          <t xml:space="preserve">trainer.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6768,7 +6768,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.earnest.seductive[1]</t>
+          <t xml:space="preserve">E1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6800,7 +6800,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.earnest.seductive[1]</t>
+          <t xml:space="preserve">E6.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6832,7 +6832,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.earnest.seductive[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6864,7 +6864,7 @@
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.earnest.seductive[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.earnest.seductive[2]</t>
+          <t xml:space="preserve">S_boycott.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6896,7 +6896,7 @@
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.earnest.seductive[1]</t>
+          <t xml:space="preserve">S_grumble.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6928,7 +6928,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.earnest.seductive[1]</t>
+          <t xml:space="preserve">S_sns.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6960,7 +6960,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.earnest.seductive[1]</t>
+          <t xml:space="preserve">S1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6992,7 +6992,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.earnest.seductive[1]</t>
+          <t xml:space="preserve">S2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7024,7 +7024,7 @@
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.earnest.seductive[1]</t>
+          <t xml:space="preserve">S3.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7056,7 +7056,7 @@
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.earnest.seductive[1]</t>
+          <t xml:space="preserve">S4_direct.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7088,7 +7088,7 @@
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.earnest.seductive[1]</t>
+          <t xml:space="preserve">S4_silent.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7120,7 +7120,7 @@
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.earnest.seductive[1]</t>
+          <t xml:space="preserve">S5.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7152,7 +7152,7 @@
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.earnest.seductive[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.earnest.seductive[1]</t>
+          <t xml:space="preserve">S6.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7184,7 +7184,7 @@
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.earnest.seductive[1]</t>
+          <t xml:space="preserve">B1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7216,7 +7216,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.earnest.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7248,7 +7248,7 @@
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.earnest.seductive[1]</t>
+          <t xml:space="preserve">B2_fighter2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7280,7 +7280,7 @@
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.earnest.seductive[1]</t>
+          <t xml:space="preserve">B4_brand.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7312,7 +7312,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.earnest.seductive[1]</t>
+          <t xml:space="preserve">B4_cm.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7344,7 +7344,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.earnest.seductive[1]</t>
+          <t xml:space="preserve">B4_fan.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7376,7 +7376,7 @@
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.earnest.seductive[1]</t>
+          <t xml:space="preserve">B4_fashion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7408,7 +7408,7 @@
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.earnest.seductive[1]</t>
+          <t xml:space="preserve">B4_gravure.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7440,7 +7440,7 @@
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.earnest.seductive[1]</t>
+          <t xml:space="preserve">B4_variety.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7472,7 +7472,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.earnest.seductive[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.earnest.seductive[1]</t>
+          <t xml:space="preserve">B4.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7504,7 +7504,7 @@
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7536,7 +7536,7 @@
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7568,7 +7568,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7600,7 +7600,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7632,7 +7632,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7664,7 +7664,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.earnest.seductive[1]</t>
+          <t xml:space="preserve">draftInterest.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7696,7 +7696,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.earnest.seductive[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7728,7 +7728,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.earnest.seductive[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7760,7 +7760,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.earnest.seductive[1]</t>
+          <t xml:space="preserve">faSigning.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7792,7 +7792,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.earnest.seductive[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7824,7 +7824,7 @@
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.earnest.seductive[1]</t>
+          <t xml:space="preserve">injury.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7856,7 +7856,7 @@
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.earnest.seductive[1]</t>
+          <t xml:space="preserve">release.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7888,7 +7888,7 @@
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.earnest.seductive[1]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7920,7 +7920,7 @@
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.earnest.seductive[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7952,7 +7952,7 @@
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.earnest.seductive[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7984,7 +7984,7 @@
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.earnest.seductive[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8016,7 +8016,7 @@
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.earnest.seductive[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8048,7 +8048,7 @@
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.earnest.seductive[1]</t>
+          <t xml:space="preserve">titleWin.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8080,7 +8080,7 @@
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8112,7 +8112,7 @@
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8144,7 +8144,7 @@
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8176,7 +8176,7 @@
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8208,7 +8208,7 @@
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8240,7 +8240,7 @@
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8944,7 +8944,7 @@
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.seductive[1]</t>
+          <t xml:space="preserve">preFinal.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8976,7 +8976,7 @@
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.earnest.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.earnest.seductive[2]</t>
+          <t xml:space="preserve">preFinal.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9008,7 +9008,7 @@
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.seductive[1]</t>
+          <t xml:space="preserve">preMatch.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9040,7 +9040,7 @@
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.earnest.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.earnest.seductive[2]</t>
+          <t xml:space="preserve">preMatch.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9072,7 +9072,7 @@
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.seductive[1]</t>
+          <t xml:space="preserve">survivor.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9104,7 +9104,7 @@
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.earnest.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.earnest.seductive[2]</t>
+          <t xml:space="preserve">survivor.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9136,7 +9136,7 @@
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.seductive[1]</t>
+          <t xml:space="preserve">champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9168,7 +9168,7 @@
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.earnest.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.earnest.seductive[2]</t>
+          <t xml:space="preserve">champion.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9200,7 +9200,7 @@
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.seductive[1]</t>
+          <t xml:space="preserve">defiant.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9232,7 +9232,7 @@
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.earnest.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.earnest.seductive[2]</t>
+          <t xml:space="preserve">defiant.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9264,7 +9264,7 @@
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.seductive[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.seductive[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9296,7 +9296,7 @@
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.earnest.seductive[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.earnest.seductive[2]</t>
+          <t xml:space="preserve">gauntlet.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9328,7 +9328,7 @@
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9360,7 +9360,7 @@
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9392,7 +9392,7 @@
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9424,7 +9424,7 @@
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.earnest.seductive[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.earnest.seductive[1]</t>
+          <t xml:space="preserve">fighter.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9456,7 +9456,7 @@
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9488,7 +9488,7 @@
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.earnest.seductive[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">

--- a/セリフ編集/キャラタイプ別/蠱惑×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×真面目.xlsx
@@ -193,7 +193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -205,7 +205,7 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="11">
         <is>
-          <t xml:space="preserve">このタイプ(蠱惑×真面目)に該当するキャラクター: 3名</t>
+          <t xml:space="preserve">このタイプ(蠱惑×真面目)に該当するキャラクター: 4名</t>
         </is>
       </c>
     </row>
@@ -235,7 +235,7 @@
     <row r="4">
       <c r="A4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">新見ゆり</t>
+          <t xml:space="preserve">長谷川レオナ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -250,19 +250,19 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">引き出し上手</t>
+          <t xml:space="preserve">人望、引き出し上手</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">飯島冴子</t>
+          <t xml:space="preserve">新見ゆり</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Submission</t>
+          <t xml:space="preserve">Allround</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
@@ -272,27 +272,49 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">忠誠心</t>
+          <t xml:space="preserve">引き出し上手</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="12">
         <is>
+          <t xml:space="preserve">飯島冴子</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Submission</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Neutral</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">忠誠心</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="12">
+        <is>
           <t xml:space="preserve">小西ゆきえ</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="2">
+      <c r="B7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Allround</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr" s="2">
+      <c r="C7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Neutral</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr" s="12">
+      <c r="D7" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">ガラスの身体、ファンサービス、早熟</t>
         </is>
@@ -306,7 +328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H287"/>
+  <dimension ref="A1:H289"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1509,7 +1531,7 @@
       </c>
       <c r="F37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここからはわたしが背負うわ</t>
+          <t xml:space="preserve">ここからは私が背負うわ</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1563,7 @@
       </c>
       <c r="F38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{partner}…わたしの力不足よ。あなたを勝たせられなかった…</t>
+          <t xml:space="preserve">{partner}…私の力不足よ。あなたを勝たせられなかった…</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2395,7 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしてもあの人とやりたくて。……聞いてくれる?</t>
+          <t xml:space="preserve">どうしてもあの人とやりたくて。……聞いてくれる？</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4027,7 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、大事な話があるの。{tenure}{record}ちゃんと評価してほしいな</t>
+          <t xml:space="preserve">社長、大事な話があるの。{tenure}{record}ちゃんと評価してほしいの</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5958,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5951,7 +5973,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.seductive.earnest[1]</t>
+          <t xml:space="preserve">autumnWarChampion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5961,14 +5983,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">準備してきたものを全部出せた。…最高の相手がいたから</t>
+          <t xml:space="preserve">仲間の奮闘を無駄にしないために、最後まで戦い抜きました。</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.seductive.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5983,7 +6005,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.earnest[1]</t>
+          <t xml:space="preserve">bestMatch.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5993,14 +6015,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王者としての誇り、毎試合で証明する。見ていてくれるかしら</t>
+          <t xml:space="preserve">準備してきたものを全部出せた。…最高の相手がいたから</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6015,7 +6037,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.seductive.earnest[1]</t>
+          <t xml:space="preserve">champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6025,14 +6047,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩たちへ。この世界には、努力した人だけが見える景色があるわ。…信じて</t>
+          <t xml:space="preserve">王者としての誇り、毎試合で証明する。見ていてくれるかしら</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.seductive.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6047,7 +6069,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.seductive.earnest[1]</t>
+          <t xml:space="preserve">hallOfFame.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6057,14 +6079,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきたものが実った。…でも、ここで止まるつもりはないわ</t>
+          <t xml:space="preserve">後輩たちへ。この世界には、努力した人だけが見える景色があるわ。…信じて</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.seductive.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6079,7 +6101,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.seductive.earnest[1]</t>
+          <t xml:space="preserve">mvp.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6089,14 +6111,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力してきたもの。…でもまだ足りないわ。もっと磨くから、見ていて</t>
+          <t xml:space="preserve">積み重ねてきたものが実った。…でも、ここで止まるつもりはないわ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6106,12 +6128,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">rookie.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6121,14 +6143,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">真剣勝負よ、今夜は</t>
+          <t xml:space="preserve">努力してきたもの。…でもまだ足りないわ。もっと磨くから、見ていて</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6138,12 +6160,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[2]</t>
+          <t xml:space="preserve">springTagChampion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6153,14 +6175,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様の前で…燃えないわけがないでしょう</t>
+          <t xml:space="preserve">相棒が背中を預けてくれたから、最後まで美しく戦えました。</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.earnest[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6175,7 +6197,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[3]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6185,14 +6207,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見ていてね、社長</t>
+          <t xml:space="preserve">真剣勝負よ、今夜は</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6202,12 +6224,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6217,14 +6239,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の熱気に、私も全力で応えたわ</t>
+          <t xml:space="preserve">満員のお客様の前で…燃えないわけがないでしょう</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.earnest[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.earnest[3]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6234,12 +6256,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[2]</t>
+          <t xml:space="preserve">seductive.earnest[3]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6249,14 +6271,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この記録、団体の誇りにしたい</t>
+          <t xml:space="preserve">…見ていてね、社長</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.earnest[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6271,7 +6293,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[3]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6281,14 +6303,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと多くのお客様を、虜にしてみせる</t>
+          <t xml:space="preserve">お客様の熱気に、私も全力で応えたわ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6298,29 +6320,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねって大事よね。もっとやりたくなっちゃう</t>
+          <t xml:space="preserve">この記録、団体の誇りにしたい</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.earnest[3]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6330,29 +6352,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[3]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と一緒だと、もっと頑張りたくなるの</t>
+          <t xml:space="preserve">次はもっと多くのお客様を、虜にしてみせる</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6367,7 +6389,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.seductive.earnest[1]</t>
+          <t xml:space="preserve">N1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6377,14 +6399,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…少し休めば、すぐ戻れるわ</t>
+          <t xml:space="preserve">積み重ねって大事よね。もっとやりたくなるわ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6399,7 +6421,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.seductive.earnest[1]</t>
+          <t xml:space="preserve">N2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6409,14 +6431,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれる人がいるって、本当に力になるの</t>
+          <t xml:space="preserve">あの人と一緒だと、もっと頑張りたくなるの</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6431,7 +6453,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.seductive.earnest[1]</t>
+          <t xml:space="preserve">N3.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6441,14 +6463,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切りたいわけじゃないの。ただ……ね</t>
+          <t xml:space="preserve">ごめんなさい…少し休めば、すぐ戻れるわ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6463,7 +6485,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.seductive.earnest[1]</t>
+          <t xml:space="preserve">N4.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6473,14 +6495,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いくら練習しても、何か足りない気がして…</t>
+          <t xml:space="preserve">応援してくれる人がいるって、本当に力になるの</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6490,29 +6512,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.seductive.earnest[1]</t>
+          <t xml:space="preserve">N5_low.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。ちゃんと結果で返すわ</t>
+          <t xml:space="preserve">裏切りたいわけじゃないの。ただ……ね</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6522,29 +6544,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.seductive.earnest[1]</t>
+          <t xml:space="preserve">N5_warning.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">思い切り鍛えられるのね。楽しみだわ</t>
+          <t xml:space="preserve">いくら練習しても、何か足りない気がして…</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6559,7 +6581,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.seductive.earnest[1]</t>
+          <t xml:space="preserve">bonus.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6569,14 +6591,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見てくれてたのね…絶対に報いるわ</t>
+          <t xml:space="preserve">ありがとう。ちゃんと結果で返すわ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6591,7 +6613,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.seductive.earnest[1]</t>
+          <t xml:space="preserve">camp.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6601,14 +6623,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう…もう一度、頑張ってみるわ</t>
+          <t xml:space="preserve">思い切り鍛えられるのね。楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6623,7 +6645,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.seductive.earnest[1]</t>
+          <t xml:space="preserve">encourage_high_trust.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6633,14 +6655,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張するけど…精一杯やるわ</t>
+          <t xml:space="preserve">ずっと見てくれてたのね…絶対に報いるわ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6655,7 +6677,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.seductive.earnest[1]</t>
+          <t xml:space="preserve">encourage.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6665,14 +6687,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お疲れ様。また明日から頑張りましょうね</t>
+          <t xml:space="preserve">ありがとう…もう一度、頑張ってみるわ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6687,7 +6709,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.seductive.earnest[1]</t>
+          <t xml:space="preserve">media.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6697,14 +6719,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が気になるけど…ありがとう。休んでくるわ</t>
+          <t xml:space="preserve">緊張するけど…精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6719,7 +6741,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.seductive.earnest[1]</t>
+          <t xml:space="preserve">party.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6729,14 +6751,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう…早く戻れるように頑張るわ</t>
+          <t xml:space="preserve">お疲れ様。また明日から頑張りましょうね</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6751,7 +6773,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.seductive.earnest[1]</t>
+          <t xml:space="preserve">refresh_leave.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6761,14 +6783,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな機会をもらえるなんて…全力で応えるわ</t>
+          <t xml:space="preserve">練習が気になるけど…ありがとう。休んでくるわ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6778,12 +6800,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.seductive.earnest[1]</t>
+          <t xml:space="preserve">special_treatment.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6793,14 +6815,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張するけど…精一杯やるわ</t>
+          <t xml:space="preserve">ありがとう…早く戻れるように頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6810,12 +6832,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.seductive.earnest[1]</t>
+          <t xml:space="preserve">trainer.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6825,14 +6847,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">義理があるから断ったけど…報告はしておくわね</t>
+          <t xml:space="preserve">こんな機会をもらえるなんて…全力で応えるわ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6847,7 +6869,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.earnest[1]</t>
+          <t xml:space="preserve">E1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6857,14 +6879,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…今日はどうしても、体が動かなくて…</t>
+          <t xml:space="preserve">緊張するけど…精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.earnest[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6879,7 +6901,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.earnest[2]</t>
+          <t xml:space="preserve">E6.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6889,14 +6911,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習に集中できないの…ごめんなさいね…</t>
+          <t xml:space="preserve">義理があるから断ったけど…報告はしておくわね</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6911,7 +6933,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.seductive.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6921,14 +6943,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「わたし、このままでいいのかしら」と後輩に弱音を漏らしている）</t>
+          <t xml:space="preserve">ごめんなさい…今日はどうしても、体が動かなくて…</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6943,7 +6965,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.seductive.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6953,14 +6975,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「わたし、ここで必要とされているのかしら」と率直な投稿）</t>
+          <t xml:space="preserve">練習に集中できないの…ごめんなさいね…</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6975,7 +6997,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.seductive.earnest[1]</t>
+          <t xml:space="preserve">S_grumble.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6985,14 +7007,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと準備してきたの。チャンスをちょうだい</t>
+          <t xml:space="preserve">（「私、このままでいいのかしら」と後輩に弱音を漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7007,7 +7029,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.seductive.earnest[1]</t>
+          <t xml:space="preserve">S_sns.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7017,14 +7039,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人を越えたいの。試合を組んでくれない？</t>
+          <t xml:space="preserve">（SNSに「私、ここで必要とされているのかしら」と率直な投稿）</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7039,7 +7061,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.seductive.earnest[1]</t>
+          <t xml:space="preserve">S1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7049,14 +7071,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">迷惑かけたくないんだけど…体が限界なの…</t>
+          <t xml:space="preserve">ずっと準備してきたの。チャンスをちょうだい</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7071,7 +7093,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.seductive.earnest[1]</t>
+          <t xml:space="preserve">S2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7081,14 +7103,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと我慢してきたの。でも、もう限界よ</t>
+          <t xml:space="preserve">あの人を越えたいの。試合を組んでくれない？</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7103,7 +7125,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.seductive.earnest[1]</t>
+          <t xml:space="preserve">S3.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7113,14 +7135,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（言いかけた言葉を、笑みの奥に飲み込んだ）</t>
+          <t xml:space="preserve">迷惑かけたくないんだけど…体が限界なの…</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7135,7 +7157,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.seductive.earnest[1]</t>
+          <t xml:space="preserve">S4_direct.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7145,14 +7167,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいの。特訓させてもらえる？</t>
+          <t xml:space="preserve">ずっと我慢してきたの。でも、もう限界よ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7167,7 +7189,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.seductive.earnest[1]</t>
+          <t xml:space="preserve">S4_silent.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7177,14 +7199,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">培ってきたものを、次の子たちに伝えたいの</t>
+          <t xml:space="preserve">…………（言いかけた言葉を、笑みの奥に飲み込んだ）</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7194,12 +7216,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.seductive.earnest[1]</t>
+          <t xml:space="preserve">S5.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7209,14 +7231,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…早く戻れるように頑張るわ</t>
+          <t xml:space="preserve">もっと強くなりたいの。特訓させてもらえる？</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7226,12 +7248,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.seductive.earnest[1]</t>
+          <t xml:space="preserve">S6.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7241,14 +7263,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と一緒じゃ仕事にならないの。何とかして</t>
+          <t xml:space="preserve">培ってきたものを、次の子たちに伝えたいの</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7263,7 +7285,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.seductive.earnest[1]</t>
+          <t xml:space="preserve">B1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7273,14 +7295,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">迷惑はかけたくないけど…あの人とはもう無理なの</t>
+          <t xml:space="preserve">ごめんなさい…早く戻れるように頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7295,7 +7317,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.seductive.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7305,14 +7327,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちゃんとブランドのイメージに合わせて取り組むわ</t>
+          <t xml:space="preserve">あの人と一緒じゃ仕事にならないの。何とかして</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7327,7 +7349,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.seductive.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7337,14 +7359,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちゃんと準備して、いい姿を見せるわ</t>
+          <t xml:space="preserve">迷惑はかけたくないけど…あの人とはもう無理なの</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7359,7 +7381,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.seductive.earnest[1]</t>
+          <t xml:space="preserve">B4_brand.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7369,14 +7391,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ひとりにちゃんと向き合う。それが大事だと思うわ</t>
+          <t xml:space="preserve">ちゃんとブランドのイメージに合わせて取り組むわ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7391,7 +7413,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.seductive.earnest[1]</t>
+          <t xml:space="preserve">B4_cm.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7401,14 +7423,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">きちんと練習して、完璧に歩いてみせるわ</t>
+          <t xml:space="preserve">ちゃんと準備して、いい姿を見せるわ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7423,7 +7445,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.seductive.earnest[1]</t>
+          <t xml:space="preserve">B4_fan.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7433,14 +7455,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">きちんと準備して、いい仕上がりにするわ</t>
+          <t xml:space="preserve">一人ひとりにちゃんと向き合う。それが大事だと思うわ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7455,7 +7477,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.seductive.earnest[1]</t>
+          <t xml:space="preserve">B4_fashion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7465,14 +7487,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちゃんと準備して、面白い話ができるよう頑張るわ</t>
+          <t xml:space="preserve">きちんと練習して、完璧に歩いてみせるわ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7487,7 +7509,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.seductive.earnest[1]</t>
+          <t xml:space="preserve">B4_gravure.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7497,14 +7519,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私でいいの？ …精一杯頑張るわ</t>
+          <t xml:space="preserve">きちんと準備して、いい仕上がりにするわ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7514,29 +7536,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">B4_variety.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道に頑張るタイプよ。見ていてくれる？</t>
+          <t xml:space="preserve">ちゃんと準備して、面白い話ができるよう頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7546,29 +7568,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">B4.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれてありがとう。期待に応えるわ</t>
+          <t xml:space="preserve">私でいいの？ …精一杯頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7578,7 +7600,7 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
@@ -7593,14 +7615,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。期待に応えるわ</t>
+          <t xml:space="preserve">地道に頑張るタイプよ。見ていてくれる？</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7610,7 +7632,7 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
@@ -7625,14 +7647,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日頑張るわ。見ていてね</t>
+          <t xml:space="preserve">選んでくれてありがとう。期待に応えるわ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7642,7 +7664,7 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
@@ -7657,14 +7679,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれてる人に申し訳ないわ…必ず戻る</t>
+          <t xml:space="preserve">ありがとう。期待に応えるわ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7674,12 +7696,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7689,14 +7711,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道に頑張るタイプよ。見ていてくれる？</t>
+          <t xml:space="preserve">毎日頑張るわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7706,12 +7728,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7721,14 +7743,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれてありがとう。期待に応えるわ</t>
+          <t xml:space="preserve">応援してくれてる人に申し訳ないわ…必ず戻る</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7743,7 +7765,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.seductive.earnest[1]</t>
+          <t xml:space="preserve">draftInterest.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7753,14 +7775,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてくれた人は久しぶりなの。…このチャンス、大事にするわ</t>
+          <t xml:space="preserve">地道に頑張るタイプよ。見ていてくれる？</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7775,7 +7797,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.seductive.earnest[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7785,14 +7807,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。期待に応えるわ</t>
+          <t xml:space="preserve">選んでくれてありがとう。期待に応えるわ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7807,7 +7829,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.seductive.earnest[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7817,14 +7839,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日頑張るわ。見ていてね</t>
+          <t xml:space="preserve">声をかけてくれた人は久しぶりなの。…このチャンス、大事にするわ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7839,7 +7861,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.earnest[1]</t>
+          <t xml:space="preserve">faSigning.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7849,14 +7871,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれてる人に申し訳ないわ…必ず戻る</t>
+          <t xml:space="preserve">ありがとう。期待に応えるわ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7871,7 +7893,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.earnest[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7881,14 +7903,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれた人たちに、申し訳ないわ…必ず見返す</t>
+          <t xml:space="preserve">毎日頑張るわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7903,7 +7925,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.seductive.earnest[1]</t>
+          <t xml:space="preserve">injury.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7913,14 +7935,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間だけど、精一杯やるわ</t>
+          <t xml:space="preserve">応援してくれてる人に申し訳ないわ…必ず戻る</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7935,7 +7957,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.seductive.earnest[1]</t>
+          <t xml:space="preserve">release.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7945,14 +7967,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">評価してくれたのね。…ちゃんと応えるわ</t>
+          <t xml:space="preserve">応援してくれた人たちに、申し訳ないわ…必ず見返す</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7967,7 +7989,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.seductive.earnest[1]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7977,14 +7999,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかったわ…でも、もう一度挑戦する</t>
+          <t xml:space="preserve">短い間だけど、精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7999,7 +8021,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.seductive.earnest[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8009,14 +8031,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できたわ…でも満足しない。もっと強くなる</t>
+          <t xml:space="preserve">評価してくれたのね。…ちゃんと応えるわ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8031,7 +8053,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.seductive.earnest[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8041,14 +8063,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった…でも、ここで終わりにはしないわ</t>
+          <t xml:space="preserve">足りなかったわ…でも、もう一度挑戦する</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8063,7 +8085,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.seductive.earnest[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8073,14 +8095,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきて…よかった。このベルト、大切にするわ</t>
+          <t xml:space="preserve">防衛できたわ…でも満足しない。もっと強くなる</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8090,12 +8112,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8105,14 +8127,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれた人たちに、申し訳ないわ…必ず見返す</t>
+          <t xml:space="preserve">足りなかった…でも、ここで終わりにはしないわ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8122,12 +8144,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">titleWin.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8137,14 +8159,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間だけど、精一杯やるわ</t>
+          <t xml:space="preserve">積み重ねてきて…よかった。このベルト、大切にするわ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8154,7 +8176,7 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
@@ -8169,14 +8191,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかったわ…でも、もう一度挑戦する</t>
+          <t xml:space="preserve">応援してくれた人たちに、申し訳ないわ…必ず見返す</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8186,7 +8208,7 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
@@ -8201,14 +8223,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できたわ…でも満足しない。もっと強くなる</t>
+          <t xml:space="preserve">短い間だけど、精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8218,7 +8240,7 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
@@ -8233,14 +8255,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった…でも、ここで終わりにはしないわ</t>
+          <t xml:space="preserve">足りなかったわ…でも、もう一度挑戦する</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8250,7 +8272,7 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
@@ -8265,14 +8287,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきて…よかった。このベルト、大切にするわ</t>
+          <t xml:space="preserve">防衛できたわ…でも満足しない。もっと強くなる</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8282,29 +8304,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この関係…直せる自信がないの…</t>
+          <t xml:space="preserve">足りなかった…でも、ここで終わりにはしないわ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8314,29 +8336,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.seductive[2]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どこで間違えたのかしら…</t>
+          <t xml:space="preserve">積み重ねてきて…よかった。このベルト、大切にするわ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8351,7 +8373,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.seductive[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8361,14 +8383,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この距離…私の何がいけなかったのかしら</t>
+          <t xml:space="preserve">この関係…直せる自信がないの…</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8383,7 +8405,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.seductive[2]</t>
+          <t xml:space="preserve">bond_39_down.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8393,14 +8415,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一度分かり合えるよう、努力しないとね</t>
+          <t xml:space="preserve">どこで間違えたのかしら…</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8415,7 +8437,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8425,14 +8447,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒のトレーニング、刺激があっていいわ</t>
+          <t xml:space="preserve">この距離…私の何がいけなかったのかしら</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8447,7 +8469,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8457,14 +8479,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒に頂点まで行きたいの。二人ならきっと届くわ</t>
+          <t xml:space="preserve">もう一度分かり合えるよう、努力しないとね</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8479,7 +8501,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">bond_60_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8489,14 +8511,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の相棒ね。この出会いに感謝してる</t>
+          <t xml:space="preserve">一緒のトレーニング、刺激があっていいわ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8511,7 +8533,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8521,14 +8543,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関係も変わったわね。前に進みましょう</t>
+          <t xml:space="preserve">一緒に頂点まで行きたいの。二人ならきっと届くわ</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8543,7 +8565,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.seductive[2]</t>
+          <t xml:space="preserve">bond_80_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8553,14 +8575,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの因縁から学んだことは多いの。次の目標を見つけなきゃ</t>
+          <t xml:space="preserve">最高の相棒ね。この出会いに感謝してる</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8575,7 +8597,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8585,14 +8607,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好敵手として意識し始めてるみたい</t>
+          <t xml:space="preserve">関係も変わったわね。前に進みましょう</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8607,7 +8629,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8617,14 +8639,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超えることが、今の一番の目標なの</t>
+          <t xml:space="preserve">あの因縁から学んだことは多いの。次の目標を見つけなきゃ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8639,7 +8661,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8649,14 +8671,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この壁を越えない限り、私に先はないわ</t>
+          <t xml:space="preserve">好敵手として意識し始めてるみたい</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8671,7 +8693,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8681,14 +8703,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最大の壁。だからこそ、越えなきゃいけないの</t>
+          <t xml:space="preserve">超えることが、今の一番の目標なの</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8703,7 +8725,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8713,14 +8735,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの存在が私を高めてくれる。これが宿命というものかしら</t>
+          <t xml:space="preserve">この壁を越えない限り、私に先はないわ</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8735,7 +8757,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8745,14 +8767,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">戦えることに感謝してる。でも次は絶対に勝つわ</t>
+          <t xml:space="preserve">最大の壁。だからこそ、越えなきゃいけないの</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8767,7 +8789,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.seductive[1]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8777,14 +8799,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体に貢献できるよう、これからも全力で努めるわ</t>
+          <t xml:space="preserve">あの存在が私を高めてくれる。これが宿命というものかしら</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8799,7 +8821,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.seductive[2]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8809,14 +8831,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでプロレスができる幸せを噛みしめてるの</t>
+          <t xml:space="preserve">戦えることに感謝してる。でも次は絶対に勝つわ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8831,7 +8853,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.seductive[1]</t>
+          <t xml:space="preserve">trust_above_75.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8841,14 +8863,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じてたのに…もうここでは頑張れないかもしれないわ</t>
+          <t xml:space="preserve">この団体に貢献できるよう、これからも全力で努めるわ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8863,7 +8885,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.seductive[2]</t>
+          <t xml:space="preserve">trust_above_75.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8873,14 +8895,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を尽くしてきたつもりよ。でも、もう…</t>
+          <t xml:space="preserve">ここでプロレスができる幸せを噛みしめてるの</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8895,7 +8917,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.seductive[1]</t>
+          <t xml:space="preserve">trust_below_20.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8905,14 +8927,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の方針に…少し不安を感じてるの</t>
+          <t xml:space="preserve">信じてたのに…もうここでは頑張れないかもしれないわ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8927,7 +8949,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.seductive[2]</t>
+          <t xml:space="preserve">trust_below_20.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8937,14 +8959,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">自分の居場所がここにあるのか…考えてしまうわ</t>
+          <t xml:space="preserve">全力を尽くしてきたつもりよ。でも、もう…</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8954,29 +8976,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.earnest[1]</t>
+          <t xml:space="preserve">trust_below_35.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">繋いでもらったこの舞台、崩す気はないの。傷ごと、立つわ</t>
+          <t xml:space="preserve">この団体の方針に…少し不安を感じてるの</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8986,29 +9008,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.earnest[2]</t>
+          <t xml:space="preserve">trust_below_35.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来た以上、最後まできっちり向き合うわ。それが筋でしょ</t>
+          <t xml:space="preserve">自分の居場所がここにあるのか…考えてしまうわ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9023,7 +9045,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.earnest[1]</t>
+          <t xml:space="preserve">preFinal.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9033,14 +9055,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手が誰でも、ちゃんと向き合うわ。手を抜くなんて、できないの</t>
+          <t xml:space="preserve">繋いでもらったこの舞台、崩す気はないの。傷ごと、立つわ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9055,7 +9077,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.earnest[2]</t>
+          <t xml:space="preserve">preFinal.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9065,14 +9087,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">繋ぐ相手がいる。だから、この一戦も手は抜けないの</t>
+          <t xml:space="preserve">ここまで来た以上、最後まできっちり向き合うわ。それが筋でしょ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9087,7 +9109,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.earnest[1]</t>
+          <t xml:space="preserve">preMatch.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9097,14 +9119,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒したわ。…でも、まだ役目の途中なの。次、出してよ。ちゃんと相手するから</t>
+          <t xml:space="preserve">相手が誰でも、ちゃんと向き合うわ。手を抜くなんて、できないの</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9119,7 +9141,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.earnest[2]</t>
+          <t xml:space="preserve">preMatch.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9129,14 +9151,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの。繋ぐまでは、退けない。次の子、来なさい</t>
+          <t xml:space="preserve">繋ぐ相手がいる。だから、この一戦も手は抜けないの</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9146,12 +9168,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.earnest[1]</t>
+          <t xml:space="preserve">survivor.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9161,14 +9183,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で紡いだ勝利よ。この結び目を、一人でほどく気はないわ</t>
+          <t xml:space="preserve">一人、倒したわ。…でも、まだ役目の途中なの。次、出してよ。ちゃんと相手するから</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9178,12 +9200,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.earnest[2]</t>
+          <t xml:space="preserve">survivor.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9193,14 +9215,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が信じてくれた……その信頼に、ちゃんと応えられたかしら</t>
+          <t xml:space="preserve">まだ立ってるの。繋ぐまでは、退けない。次の子、来なさい</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9215,7 +9237,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.earnest[1]</t>
+          <t xml:space="preserve">champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9225,14 +9247,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞は嬉しいわ。でも……本当に欲しかったのは、三人で掴む勝利</t>
+          <t xml:space="preserve">三人で紡いだ勝利よ。この結び目を、一人でほどく気はないわ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9247,7 +9269,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.earnest[2]</t>
+          <t xml:space="preserve">champion.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9257,14 +9279,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった分は、次に全て返す。約束するわ</t>
+          <t xml:space="preserve">仲間が信じてくれた……その信頼に、ちゃんと応えられたかしら</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9279,7 +9301,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.earnest[1]</t>
+          <t xml:space="preserve">defiant.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9289,14 +9311,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人一人、ちゃんと向き合ったわ。この身体で返した答えよ</t>
+          <t xml:space="preserve">賞は嬉しいわ。でも……本当に欲しかったのは、三人で掴む勝利</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9311,7 +9333,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.earnest[2]</t>
+          <t xml:space="preserve">defiant.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9321,14 +9343,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界なんて何度も見えた。でも……ここで崩れるのは、許せなかったの</t>
+          <t xml:space="preserve">足りなかった分は、次に全て返す。約束するわ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9338,12 +9360,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9353,14 +9375,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でいくわ。最高の試合にしましょう</t>
+          <t xml:space="preserve">一人一人、ちゃんと向き合ったわ。この身体で返した答えよ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9370,12 +9392,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9385,14 +9407,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られたのは、支えてくれた皆のおかげよ。…ありがとう</t>
+          <t xml:space="preserve">限界なんて何度も見えた。でも……ここで崩れるのは、許せなかったの</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9402,7 +9424,7 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
@@ -9417,14 +9439,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体のために戦えて…嬉しいわ</t>
+          <t xml:space="preserve">全力でいくわ。最高の試合にしましょう</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.earnest[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9434,29 +9456,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきた全部が報われた…泣きそうだわ</t>
+          <t xml:space="preserve">ここまで来られたのは、支えてくれた皆のおかげよ。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9466,7 +9488,7 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
@@ -9476,49 +9498,113 @@
       </c>
       <c r="E286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてくれた人は久しぶりなの。…このチャンス、大事にするわ</t>
+          <t xml:space="preserve">団体のために戦えて…嬉しいわ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">積み重ねてきた全部が報われた…泣きそうだわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてくれた人は久しぶりなの。…このチャンス、大事にするわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.earnest[1]</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr" s="2">
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr" s="12">
+      <c r="D289" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr" s="2">
+      <c r="E289" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr" s="3">
+      <c r="F289" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">評価してくれたのね。…ちゃんと応えるわ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H287"/>
+  <autoFilter ref="A1:H289"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×真面目.xlsx
@@ -328,7 +328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H289"/>
+  <dimension ref="A1:H296"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3906,7 +3906,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.seductive.earnest[1]</t>
+          <t xml:space="preserve">decline_accept.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3931,14 +3931,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。…期待に応えるからね。見ててね。</t>
+          <t xml:space="preserve">妥当な線ね。……下がったぶんは、技のほうで埋めるわ。見ていて。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.seductive.earnest[1]</t>
+          <t xml:space="preserve">decline_hold.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3963,14 +3963,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……分かったわ。社長の判断だもの、尊重する。この額で、精一杯やるからね。</t>
+          <t xml:space="preserve">……そこまでしてくれるの。……なら、値段の話は今年で終わりにするわ。上げさせてみせる。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.seductive.earnest[1]</t>
+          <t xml:space="preserve">decline_open.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……残念ね。でも了解したわ。ただ、この判断のことは覚えておいてね。</t>
+          <t xml:space="preserve">……分かるわ。自分の身体のことだもの。数字より先に、こちらが気づいてる。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.seductive.earnest[1]</t>
+          <t xml:space="preserve">decline_strict.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4027,14 +4027,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、大事な話があるの。{tenure}{record}ちゃんと評価してほしいの</t>
+          <t xml:space="preserve">……理屈は通ってるわ。通りすぎているくらい。……ええ、覚えておく。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.seductive.earnest[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4059,14 +4059,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知したわ。でもね、このまま変わらないなら……いずれ考えを改めることになるの。</t>
+          <t xml:space="preserve">これでいいわ。……身の丈を知ってる女のほうが、長く使えるでしょう？</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.seductive.earnest[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4091,14 +4091,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、長い間お世話になったわ。でも、もうここでは続けられないの。</t>
+          <t xml:space="preserve">……据え置く理由が見当たらないわ。……なら、その理由をこちらで作るまでね。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.earnest[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.seductive.earnest[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4123,14 +4123,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">自分なりに、ずっと考えてきたのよ。……ここを去ることにするわ。</t>
+          <t xml:space="preserve">{tenure}自分の身体は自分が一番よく観ているの。……今年は下げて。それが筋だと思うわ。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.seductive.earnest[1]</t>
+          <t xml:space="preserve">raise_accept.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4155,14 +4155,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。{record}自分なりに考えた結果なの。ここでの経験には感謝してる。でも……新しい場所で挑戦したいのよ。</t>
+          <t xml:space="preserve">ありがとう。…期待に応えるからね。見ててね。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.seductive.earnest[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4187,14 +4187,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。{tenure}ここで過ごした時間は大切よ。でも…次の場所を見つけたいの。</t>
+          <t xml:space="preserve">……分かったわ。社長の判断だもの、尊重する。この額で、精一杯やるからね。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.seductive.earnest[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4219,14 +4219,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……承知したわ。{tenure_farewell}ここで過ごした日々には、感謝してるの。{rivalry}</t>
+          <t xml:space="preserve">……残念ね。でも了解したわ。ただ、この判断のことは覚えておいてね。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.seductive.earnest[1]</t>
+          <t xml:space="preserve">raise_open.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4251,14 +4251,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お気持ちは嬉しいの……。でもこの決断は、ずっと考え抜いた末のものよ。ごめんなさい。</t>
+          <t xml:space="preserve">社長、大事な話があるの。{tenure}{record}ちゃんと評価してほしいの</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.earnest[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.seductive.earnest[1]</t>
+          <t xml:space="preserve">raise_refuse.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4283,370 +4283,370 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長の誠意、ちゃんと受け取ったわ。もう一度、ここで全力を出すからね。</t>
+          <t xml:space="preserve">……承知したわ。でもね、このまま変わらないなら……いずれ考えを改めることになるの。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、長い間お世話になったわ。でも、もうここでは続けられないの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.seductive.earnest[2]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.seductive.earnest[2]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">自分なりに、ずっと考えてきたのよ。……ここを去ることにするわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとう。{record}自分なりに考えた結果なの。ここでの経験には感謝してる。でも……新しい場所で挑戦したいのよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。{tenure}ここで過ごした時間は大切よ。でも…次の場所を見つけたいの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……承知したわ。{tenure_farewell}ここで過ごした日々には、感謝してるの。{rivalry}</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お気持ちは嬉しいの……。でもこの決断は、ずっと考え抜いた末のものよ。ごめんなさい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……社長の誠意、ちゃんと受け取ったわ。もう一度、ここで全力を出すからね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.seductive.earnest[1]</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr" s="12">
+      <c r="D131" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.seductive.earnest[1]</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr" s="2">
+      <c r="E131" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr" s="3">
+      <c r="F131" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">今の仲間を途中で捨てるなんて、私には考えられない。
 …ごめんなさい</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.seductive.earnest[1]</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr" s="12">
+      <c r="D132" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.seductive.earnest[1]</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr" s="2">
+      <c r="E132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr" s="3">
+      <c r="F132" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">みんなを置いて行くわけにはいかないの。
 …ごめんなさい</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.seductive.earnest[1]</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr" s="12">
+      <c r="D133" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.seductive.earnest[1]</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr" s="2">
+      <c r="E133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr" s="3">
+      <c r="F133" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">この団体を離れるのは簡単じゃないの。
 …でも、聞くだけなら</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.seductive.earnest[1]</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr" s="12">
+      <c r="D134" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.seductive.earnest[1]</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr" s="2">
+      <c r="E134" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr" s="3">
+      <c r="F134" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">新しい仲間のために…全力を尽くすわ。
 よろしくね</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちのメンバーのこと、もう少しだけ目を向けてくださいませんか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、次の興行のメイン、私に預けてくれませんか。手応えはあるんです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちの仕事に見合うお手当て、考え直してくださいませんか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="40" customHeight="1">
-      <c r="A131" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私の仕事、届いてるなら一言ください。それで救われる子もいるんです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="40" customHeight="1">
-      <c r="A132" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、ありがとうございます。お言葉、ちゃんと持って帰ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="40" customHeight="1">
-      <c r="A133" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…承知しました。出過ぎた口きいて、すみません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="40" customHeight="1">
-      <c r="A134" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.earnest[1]</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
-        </is>
-      </c>
-    </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4671,14 +4671,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ありがとうございます。預かった以上、手は抜きません。</t>
+          <t xml:space="preserve">社長、私たちのメンバーのこと、もう少しだけ目を向けてくださいませんか。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4703,14 +4703,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。図々しいことを言いました。</t>
+          <t xml:space="preserve">社長、次の興行のメイン、私に預けてくれませんか。手応えはあるんです。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4735,14 +4735,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、お気遣いありがとうございます。</t>
+          <t xml:space="preserve">社長、私たちの仕事に見合うお手当て、考え直してくださいませんか。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4767,14 +4767,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ありがとうございます。きちんと結果でお返しします。</t>
+          <t xml:space="preserve">社長、私の仕事、届いてるなら一言ください。それで救われる子もいるんです。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4799,14 +4799,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。お金の話、出してすみません。</t>
+          <t xml:space="preserve">社長、ありがとうございます。お言葉、ちゃんと持って帰ります。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4831,14 +4831,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
+          <t xml:space="preserve">…承知しました。出過ぎた口きいて、すみません。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4863,14 +4863,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ありがとうございます。お言葉、ちゃんと持って帰ります。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4895,14 +4895,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。出過ぎたこと言いました。</t>
+          <t xml:space="preserve">社長、ありがとうございます。預かった以上、手は抜きません。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4927,14 +4927,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
+          <t xml:space="preserve">…承知しました。図々しいことを言いました。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4959,14 +4959,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい。輪の外にいる子の気持ち、見えてなかった。</t>
+          <t xml:space="preserve">…社長、お気遣いありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4991,14 +4991,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。甘え過ぎないようにします。</t>
+          <t xml:space="preserve">社長、ありがとうございます。きちんと結果でお返しします。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5023,14 +5023,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい、配慮が足りませんでした。</t>
+          <t xml:space="preserve">…承知しました。お金の話、出してすみません。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5055,14 +5055,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5087,14 +5087,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい。リング外まで持ち込んだのは、やりすぎでした。</t>
+          <t xml:space="preserve">社長、ありがとうございます。お言葉、ちゃんと持って帰ります。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5119,14 +5119,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとうします。</t>
+          <t xml:space="preserve">…承知しました。出過ぎたこと言いました。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5151,14 +5151,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。立場ある身で、本当に恥ずかしい。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5183,14 +5183,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ありがとうございます。次はちゃんとします。</t>
+          <t xml:space="preserve">…ごめんなさい。輪の外にいる子の気持ち、見えてなかった。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5215,14 +5215,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ご配慮ありがとうございます。</t>
+          <t xml:space="preserve">…ありがとうございます。甘え過ぎないようにします。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5247,14 +5247,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。ご厚意、頂戴します。</t>
+          <t xml:space="preserve">…ごめんなさい、配慮が足りませんでした。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5279,14 +5279,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご心配ありがとうございます。まだ立てます。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5311,14 +5311,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。皆に支えてもらえます。</t>
+          <t xml:space="preserve">…ごめんなさい。リング外まで持ち込んだのは、やりすぎでした。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5343,14 +5343,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい。私の目が届いてなかった。</t>
+          <t xml:space="preserve">…ありがとうございます。役柄の責任、まっとうします。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5375,14 +5375,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ありがとうございます。穏便にいきます。</t>
+          <t xml:space="preserve">…申し訳ありません。立場ある身で、本当に恥ずかしい。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5407,14 +5407,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。下の子も救われます。</t>
+          <t xml:space="preserve">…社長、ありがとうございます。次はちゃんとします。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5439,14 +5439,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい。わかりやすかったかな。</t>
+          <t xml:space="preserve">…社長、ご配慮ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5471,14 +5471,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…静かに目を伏せた）</t>
+          <t xml:space="preserve">…ありがとうございます。ご厚意、頂戴します。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5503,14 +5503,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
+          <t xml:space="preserve">…ご心配ありがとうございます。まだ立てます。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5535,14 +5535,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんなさい。私の判断が行きすぎてました。</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。皆に支えてもらえます。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5567,14 +5567,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、ありがとうございます。責任は私が持ちます。</t>
+          <t xml:space="preserve">…ごめんなさい。私の目が届いてなかった。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5599,14 +5599,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。私の見落とし、拾ってくれて。</t>
+          <t xml:space="preserve">…社長、ありがとうございます。穏便にいきます。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.attack.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5631,14 +5631,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">けじめを、つけさせて</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。下の子も救われます。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.seductive</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest.defend.seductive</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5663,14 +5663,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるつもりはないわ</t>
+          <t xml:space="preserve">…ごめんなさい。わかりやすかったかな。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5680,29 +5680,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が実を結んだわ…まだ上を目指すわよ</t>
+          <t xml:space="preserve">（…静かに目を伏せた）</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5712,29 +5712,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきたものが…形になりそうなの</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お気持ち、受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5744,29 +5744,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日道場に来るのが…こんなに辛いなんてね</t>
+          <t xml:space="preserve">…ごめんなさい。私の判断が行きすぎてました。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5776,29 +5776,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">闘う気持ちを忘れてたわ…でもね、もう迷わない</t>
+          <t xml:space="preserve">…社長、ありがとうございます。責任は私が持ちます。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5808,29 +5808,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">迷惑かけた分…返すわ、倍にしてね</t>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。私の見落とし、拾ってくれて。</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.earnest[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.attack.seductive</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5840,29 +5840,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.seductive.earnest[1]</t>
+          <t xml:space="preserve">earnest.attack.seductive</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの負けから…ずっと考えてるの、何がいけなかったのかって</t>
+          <t xml:space="preserve">けじめを、つけさせて</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.seductive.earnest[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.earnest.defend.seductive</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5872,29 +5872,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.seductive.earnest[1]</t>
+          <t xml:space="preserve">earnest.defend.seductive</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できたのに…まだ足りないの</t>
+          <t xml:space="preserve">逃げるつもりはないわ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.seductive.earnest[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5919,14 +5919,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">復帰できた…でもね、体が覚えてるの、あの痛みを</t>
+          <t xml:space="preserve">練習が実を結んだわ…まだ上を目指すわよ</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.seductive.earnest[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5951,14 +5951,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我は治ったわ。でもね、離れていた時間が…重いの</t>
+          <t xml:space="preserve">積み重ねてきたものが…形になりそうなの</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.earnest[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5968,29 +5968,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間の奮闘を無駄にしないために、最後まで戦い抜きました。</t>
+          <t xml:space="preserve">毎日道場に来るのが…こんなに辛いなんてね</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.earnest[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -6000,29 +6000,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">準備してきたものを全部出せた。…最高の相手がいたから</t>
+          <t xml:space="preserve">闘う気持ちを忘れてたわ…でもね、もう迷わない</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.seductive.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6032,29 +6032,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">王者としての誇り、毎試合で証明する。見ていてくれるかしら</t>
+          <t xml:space="preserve">迷惑かけた分…返すわ、倍にしてね</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6064,29 +6064,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.seductive.earnest[1]</t>
+          <t xml:space="preserve">defeat.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩たちへ。この世界には、努力した人だけが見える景色があるわ。…信じて</t>
+          <t xml:space="preserve">あの負けから…ずっと考えてるの、何がいけなかったのかって</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.seductive.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6096,29 +6096,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.seductive.earnest[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきたものが実った。…でも、ここで止まるつもりはないわ</t>
+          <t xml:space="preserve">復帰できたのに…まだ足りないの</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.seductive.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6128,29 +6128,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.seductive.earnest[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">努力してきたもの。…でもまだ足りないわ。もっと磨くから、見ていて</t>
+          <t xml:space="preserve">復帰できた…でもね、体が覚えてるの、あの痛みを</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.earnest[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6160,29 +6160,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.seductive.earnest[1]</t>
+          <t xml:space="preserve">penalty_end.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒が背中を預けてくれたから、最後まで美しく戦えました。</t>
+          <t xml:space="preserve">怪我は治ったわ。でもね、離れていた時間が…重いの</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">autumnWarChampion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6207,14 +6207,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">真剣勝負よ、今夜は</t>
+          <t xml:space="preserve">仲間の奮闘を無駄にしないために、最後まで戦い抜きました。</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[2]</t>
+          <t xml:space="preserve">bestMatch.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6239,14 +6239,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員のお客様の前で…燃えないわけがないでしょう</t>
+          <t xml:space="preserve">準備してきたものを全部出せた。…最高の相手がいたから</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.earnest[3]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[3]</t>
+          <t xml:space="preserve">champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6271,14 +6271,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見ていてね、社長</t>
+          <t xml:space="preserve">王者としての誇り、毎試合で証明する。見ていてくれるかしら</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">hallOfFame.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6303,14 +6303,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様の熱気に、私も全力で応えたわ</t>
+          <t xml:space="preserve">後輩たちへ。この世界には、努力した人だけが見える景色があるわ。…信じて</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.earnest[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[2]</t>
+          <t xml:space="preserve">mvp.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6335,14 +6335,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この記録、団体の誇りにしたい</t>
+          <t xml:space="preserve">積み重ねてきたものが実った。…でも、ここで止まるつもりはないわ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.earnest[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[3]</t>
+          <t xml:space="preserve">rookie.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6367,14 +6367,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと多くのお客様を、虜にしてみせる</t>
+          <t xml:space="preserve">努力してきたもの。…でもまだ足りないわ。もっと磨くから、見ていて</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.earnest[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6384,29 +6384,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.seductive.earnest[1]</t>
+          <t xml:space="preserve">springTagChampion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねって大事よね。もっとやりたくなるわ</t>
+          <t xml:space="preserve">相棒が背中を預けてくれたから、最後まで美しく戦えました。</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6416,29 +6416,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と一緒だと、もっと頑張りたくなるの</t>
+          <t xml:space="preserve">真剣勝負よ、今夜は</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6448,29 +6448,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…少し休めば、すぐ戻れるわ</t>
+          <t xml:space="preserve">満員のお客様の前で…燃えないわけがないでしょう</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.earnest[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.seductive.earnest[3]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6480,29 +6480,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[3]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれる人がいるって、本当に力になるの</t>
+          <t xml:space="preserve">…見ていてね、社長</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6512,29 +6512,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">裏切りたいわけじゃないの。ただ……ね</t>
+          <t xml:space="preserve">お客様の熱気に、私も全力で応えたわ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6544,29 +6544,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いくら練習しても、何か足りない気がして…</t>
+          <t xml:space="preserve">この記録、団体の誇りにしたい</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.earnest[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.seductive.earnest[3]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6576,29 +6576,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[3]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。ちゃんと結果で返すわ</t>
+          <t xml:space="preserve">次はもっと多くのお客様を、虜にしてみせる</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6608,29 +6608,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.seductive.earnest[1]</t>
+          <t xml:space="preserve">N1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">思い切り鍛えられるのね。楽しみだわ</t>
+          <t xml:space="preserve">積み重ねって大事よね。もっとやりたくなるわ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6640,29 +6640,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.seductive.earnest[1]</t>
+          <t xml:space="preserve">N2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見てくれてたのね…絶対に報いるわ</t>
+          <t xml:space="preserve">あの人と一緒だと、もっと頑張りたくなるの</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6672,29 +6672,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.seductive.earnest[1]</t>
+          <t xml:space="preserve">N3.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう…もう一度、頑張ってみるわ</t>
+          <t xml:space="preserve">ごめんなさい…少し休めば、すぐ戻れるわ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6704,29 +6704,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.seductive.earnest[1]</t>
+          <t xml:space="preserve">N4.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張するけど…精一杯やるわ</t>
+          <t xml:space="preserve">応援してくれる人がいるって、本当に力になるの</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6736,29 +6736,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.seductive.earnest[1]</t>
+          <t xml:space="preserve">N5_low.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お疲れ様。また明日から頑張りましょうね</t>
+          <t xml:space="preserve">裏切りたいわけじゃないの。ただ……ね</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.earnest[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6768,29 +6768,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.seductive.earnest[1]</t>
+          <t xml:space="preserve">N5_warning.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が気になるけど…ありがとう。休んでくるわ</t>
+          <t xml:space="preserve">いくら練習しても、何か足りない気がして…</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.seductive.earnest[1]</t>
+          <t xml:space="preserve">bonus.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6815,14 +6815,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう…早く戻れるように頑張るわ</t>
+          <t xml:space="preserve">ありがとう。ちゃんと結果で返すわ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.seductive.earnest[1]</t>
+          <t xml:space="preserve">camp.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6847,14 +6847,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな機会をもらえるなんて…全力で応えるわ</t>
+          <t xml:space="preserve">思い切り鍛えられるのね。楽しみだわ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6864,12 +6864,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.seductive.earnest[1]</t>
+          <t xml:space="preserve">encourage_high_trust.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6879,14 +6879,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張するけど…精一杯やるわ</t>
+          <t xml:space="preserve">ずっと見てくれてたのね…絶対に報いるわ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6896,12 +6896,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.seductive.earnest[1]</t>
+          <t xml:space="preserve">encourage.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6911,14 +6911,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">義理があるから断ったけど…報告はしておくわね</t>
+          <t xml:space="preserve">ありがとう…もう一度、頑張ってみるわ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.earnest[1]</t>
+          <t xml:space="preserve">media.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6943,14 +6943,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…今日はどうしても、体が動かなくて…</t>
+          <t xml:space="preserve">緊張するけど…精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.earnest[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.seductive.earnest[2]</t>
+          <t xml:space="preserve">party.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6975,14 +6975,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習に集中できないの…ごめんなさいね…</t>
+          <t xml:space="preserve">お疲れ様。また明日から頑張りましょうね</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.seductive.earnest[1]</t>
+          <t xml:space="preserve">refresh_leave.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7007,14 +7007,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「私、このままでいいのかしら」と後輩に弱音を漏らしている）</t>
+          <t xml:space="preserve">練習が気になるけど…ありがとう。休んでくるわ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.seductive.earnest[1]</t>
+          <t xml:space="preserve">special_treatment.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7039,14 +7039,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「私、ここで必要とされているのかしら」と率直な投稿）</t>
+          <t xml:space="preserve">ありがとう…早く戻れるように頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.earnest[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7056,12 +7056,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.seductive.earnest[1]</t>
+          <t xml:space="preserve">trainer.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7071,14 +7071,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと準備してきたの。チャンスをちょうだい</t>
+          <t xml:space="preserve">こんな機会をもらえるなんて…全力で応えるわ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.seductive.earnest[1]</t>
+          <t xml:space="preserve">E1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7103,14 +7103,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人を越えたいの。試合を組んでくれない？</t>
+          <t xml:space="preserve">緊張するけど…精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.seductive.earnest[1]</t>
+          <t xml:space="preserve">E6.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7135,14 +7135,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">迷惑かけたくないんだけど…体が限界なの…</t>
+          <t xml:space="preserve">義理があるから断ったけど…報告はしておくわね</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.seductive.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7167,14 +7167,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと我慢してきたの。でも、もう限界よ</t>
+          <t xml:space="preserve">ごめんなさい…今日はどうしても、体が動かなくて…</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.seductive.earnest[1]</t>
+          <t xml:space="preserve">S_boycott.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7199,14 +7199,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（言いかけた言葉を、笑みの奥に飲み込んだ）</t>
+          <t xml:space="preserve">練習に集中できないの…ごめんなさいね…</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.seductive.earnest[1]</t>
+          <t xml:space="preserve">S_grumble.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7231,14 +7231,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと強くなりたいの。特訓させてもらえる？</t>
+          <t xml:space="preserve">（「私、このままでいいのかしら」と後輩に弱音を漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.seductive.earnest[1]</t>
+          <t xml:space="preserve">S_sns.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7263,14 +7263,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">培ってきたものを、次の子たちに伝えたいの</t>
+          <t xml:space="preserve">（SNSに「私、ここで必要とされているのかしら」と率直な投稿）</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.seductive.earnest[1]</t>
+          <t xml:space="preserve">S1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7295,14 +7295,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…早く戻れるように頑張るわ</t>
+          <t xml:space="preserve">ずっと準備してきたの。チャンスをちょうだい</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.seductive.earnest[1]</t>
+          <t xml:space="preserve">S2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7327,14 +7327,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人と一緒じゃ仕事にならないの。何とかして</t>
+          <t xml:space="preserve">あの人を越えたいの。試合を組んでくれない？</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.seductive.earnest[1]</t>
+          <t xml:space="preserve">S3.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7359,14 +7359,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">迷惑はかけたくないけど…あの人とはもう無理なの</t>
+          <t xml:space="preserve">迷惑かけたくないんだけど…体が限界なの…</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.seductive.earnest[1]</t>
+          <t xml:space="preserve">S4_direct.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7391,14 +7391,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちゃんとブランドのイメージに合わせて取り組むわ</t>
+          <t xml:space="preserve">ずっと我慢してきたの。でも、もう限界よ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.seductive.earnest[1]</t>
+          <t xml:space="preserve">S4_silent.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7423,14 +7423,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちゃんと準備して、いい姿を見せるわ</t>
+          <t xml:space="preserve">…………（言いかけた言葉を、笑みの奥に飲み込んだ）</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7440,12 +7440,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.seductive.earnest[1]</t>
+          <t xml:space="preserve">S5.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7455,14 +7455,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人ひとりにちゃんと向き合う。それが大事だと思うわ</t>
+          <t xml:space="preserve">もっと強くなりたいの。特訓させてもらえる？</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.earnest[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.seductive.earnest[1]</t>
+          <t xml:space="preserve">S6.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7487,14 +7487,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">きちんと練習して、完璧に歩いてみせるわ</t>
+          <t xml:space="preserve">培ってきたものを、次の子たちに伝えたいの</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.seductive.earnest[1]</t>
+          <t xml:space="preserve">B1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7519,14 +7519,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">きちんと準備して、いい仕上がりにするわ</t>
+          <t xml:space="preserve">ごめんなさい…早く戻れるように頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.seductive.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter1.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7551,14 +7551,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちゃんと準備して、面白い話ができるよう頑張るわ</t>
+          <t xml:space="preserve">あの人と一緒じゃ仕事にならないの。何とかして</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.seductive.earnest[1]</t>
+          <t xml:space="preserve">B2_fighter2.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7583,14 +7583,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私でいいの？ …精一杯頑張るわ</t>
+          <t xml:space="preserve">迷惑はかけたくないけど…あの人とはもう無理なの</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7600,29 +7600,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">B4_brand.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道に頑張るタイプよ。見ていてくれる？</t>
+          <t xml:space="preserve">ちゃんとブランドのイメージに合わせて取り組むわ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7632,29 +7632,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">B4_cm.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれてありがとう。期待に応えるわ</t>
+          <t xml:space="preserve">ちゃんと準備して、いい姿を見せるわ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7664,29 +7664,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">B4_fan.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。期待に応えるわ</t>
+          <t xml:space="preserve">一人ひとりにちゃんと向き合う。それが大事だと思うわ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7696,29 +7696,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">B4_fashion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日頑張るわ。見ていてね</t>
+          <t xml:space="preserve">きちんと練習して、完璧に歩いてみせるわ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7728,29 +7728,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">B4_gravure.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれてる人に申し訳ないわ…必ず戻る</t>
+          <t xml:space="preserve">きちんと準備して、いい仕上がりにするわ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7760,29 +7760,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.seductive.earnest[1]</t>
+          <t xml:space="preserve">B4_variety.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">地道に頑張るタイプよ。見ていてくれる？</t>
+          <t xml:space="preserve">ちゃんと準備して、面白い話ができるよう頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.earnest[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7792,29 +7792,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.seductive.earnest[1]</t>
+          <t xml:space="preserve">B4.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくれてありがとう。期待に応えるわ</t>
+          <t xml:space="preserve">私でいいの？ …精一杯頑張るわ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7839,14 +7839,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてくれた人は久しぶりなの。…このチャンス、大事にするわ</t>
+          <t xml:space="preserve">地道に頑張るタイプよ。見ていてくれる？</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7871,14 +7871,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。期待に応えるわ</t>
+          <t xml:space="preserve">選んでくれてありがとう。期待に応えるわ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7888,12 +7888,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7903,14 +7903,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">毎日頑張るわ。見ていてね</t>
+          <t xml:space="preserve">ありがとう。期待に応えるわ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7935,14 +7935,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれてる人に申し訳ないわ…必ず戻る</t>
+          <t xml:space="preserve">毎日頑張るわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7952,12 +7952,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.seductive.earnest[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7967,14 +7967,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">応援してくれた人たちに、申し訳ないわ…必ず見返す</t>
+          <t xml:space="preserve">応援してくれてる人に申し訳ないわ…必ず戻る</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.seductive.earnest[1]</t>
+          <t xml:space="preserve">draftInterest.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7999,14 +7999,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間だけど、精一杯やるわ</t>
+          <t xml:space="preserve">地道に頑張るタイプよ。見ていてくれる？</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.seductive.earnest[1]</t>
+          <t xml:space="preserve">draftJoin.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8031,14 +8031,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">評価してくれたのね。…ちゃんと応えるわ</t>
+          <t xml:space="preserve">選んでくれてありがとう。期待に応えるわ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.seductive.earnest[1]</t>
+          <t xml:space="preserve">faGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8063,14 +8063,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかったわ…でも、もう一度挑戦する</t>
+          <t xml:space="preserve">声をかけてくれた人は久しぶりなの。…このチャンス、大事にするわ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.seductive.earnest[1]</t>
+          <t xml:space="preserve">faSigning.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8095,14 +8095,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できたわ…でも満足しない。もっと強くなる</t>
+          <t xml:space="preserve">ありがとう。期待に応えるわ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.seductive.earnest[1]</t>
+          <t xml:space="preserve">faWelcome.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8127,14 +8127,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった…でも、ここで終わりにはしないわ</t>
+          <t xml:space="preserve">毎日頑張るわ。見ていてね</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.seductive.earnest[1]</t>
+          <t xml:space="preserve">injury.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8159,14 +8159,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきて…よかった。このベルト、大切にするわ</t>
+          <t xml:space="preserve">応援してくれてる人に申し訳ないわ…必ず戻る</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">release.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8198,7 +8198,7 @@
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">rentalGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8230,7 +8230,7 @@
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">scoutGreeting.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8255,14 +8255,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかったわ…でも、もう一度挑戦する</t>
+          <t xml:space="preserve">評価してくれたのね。…ちゃんと応えるわ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8287,14 +8287,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛できたわ…でも満足しない。もっと強くなる</t>
+          <t xml:space="preserve">足りなかったわ…でも、もう一度挑戦する</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">titleDefense.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8319,14 +8319,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった…でも、ここで終わりにはしないわ</t>
+          <t xml:space="preserve">防衛できたわ…でも満足しない。もっと強くなる</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">titleLoss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8351,14 +8351,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきて…よかった。このベルト、大切にするわ</t>
+          <t xml:space="preserve">足りなかった…でも、ここで終わりにはしないわ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8368,29 +8368,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.seductive[1]</t>
+          <t xml:space="preserve">titleWin.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この関係…直せる自信がないの…</t>
+          <t xml:space="preserve">積み重ねてきて…よかった。このベルト、大切にするわ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.seductive[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8400,29 +8400,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.earnest.seductive[2]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どこで間違えたのかしら…</t>
+          <t xml:space="preserve">応援してくれた人たちに、申し訳ないわ…必ず見返す</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8432,29 +8432,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この距離…私の何がいけなかったのかしら</t>
+          <t xml:space="preserve">短い間だけど、精一杯やるわ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8464,29 +8464,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.earnest.seductive[2]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一度分かり合えるよう、努力しないとね</t>
+          <t xml:space="preserve">足りなかったわ…でも、もう一度挑戦する</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8496,29 +8496,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒のトレーニング、刺激があっていいわ</t>
+          <t xml:space="preserve">防衛できたわ…でも満足しない。もっと強くなる</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8528,29 +8528,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒に頂点まで行きたいの。二人ならきっと届くわ</t>
+          <t xml:space="preserve">足りなかった…でも、ここで終わりにはしないわ</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8560,29 +8560,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の相棒ね。この出会いに感謝してる</t>
+          <t xml:space="preserve">積み重ねてきて…よかった。このベルト、大切にするわ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.seductive[1]</t>
+          <t xml:space="preserve">bond_39_down.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8607,14 +8607,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関係も変わったわね。前に進みましょう</t>
+          <t xml:space="preserve">この関係…直せる自信がないの…</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.earnest.seductive[2]</t>
+          <t xml:space="preserve">bond_39_down.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8639,14 +8639,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの因縁から学んだことは多いの。次の目標を見つけなきゃ</t>
+          <t xml:space="preserve">どこで間違えたのかしら…</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">bond_59_down.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8671,14 +8671,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">好敵手として意識し始めてるみたい</t>
+          <t xml:space="preserve">この距離…私の何がいけなかったのかしら</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">bond_59_down.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8703,14 +8703,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超えることが、今の一番の目標なの</t>
+          <t xml:space="preserve">もう一度分かり合えるよう、努力しないとね</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">bond_60_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8735,14 +8735,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この壁を越えない限り、私に先はないわ</t>
+          <t xml:space="preserve">一緒のトレーニング、刺激があっていいわ</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">bond_80_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8767,14 +8767,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最大の壁。だからこそ、越えなきゃいけないの</t>
+          <t xml:space="preserve">一緒に頂点まで行きたいの。二人ならきっと届くわ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.seductive[1]</t>
+          <t xml:space="preserve">bond_80_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8799,14 +8799,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの存在が私を高めてくれる。これが宿命というものかしら</t>
+          <t xml:space="preserve">最高の相棒ね。この出会いに感謝してる</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.earnest.seductive[2]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8831,14 +8831,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">戦えることに感謝してる。でも次は絶対に勝つわ</t>
+          <t xml:space="preserve">関係も変わったわね。前に進みましょう</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.seductive[1]</t>
+          <t xml:space="preserve">rivalry_29_down.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8863,14 +8863,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体に貢献できるよう、これからも全力で努めるわ</t>
+          <t xml:space="preserve">あの因縁から学んだことは多いの。次の目標を見つけなきゃ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.earnest.seductive[2]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8895,14 +8895,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここでプロレスができる幸せを噛みしめてるの</t>
+          <t xml:space="preserve">好敵手として意識し始めてるみたい</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.seductive[1]</t>
+          <t xml:space="preserve">rivalry_30_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8927,14 +8927,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じてたのに…もうここでは頑張れないかもしれないわ</t>
+          <t xml:space="preserve">超えることが、今の一番の目標なの</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.earnest.seductive[2]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8959,14 +8959,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を尽くしてきたつもりよ。でも、もう…</t>
+          <t xml:space="preserve">この壁を越えない限り、私に先はないわ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.seductive[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.seductive[1]</t>
+          <t xml:space="preserve">rivalry_50_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8991,14 +8991,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の方針に…少し不安を感じてるの</t>
+          <t xml:space="preserve">最大の壁。だからこそ、越えなきゃいけないの</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.seductive[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.earnest.seductive[2]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9023,14 +9023,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">自分の居場所がここにあるのか…考えてしまうわ</t>
+          <t xml:space="preserve">あの存在が私を高めてくれる。これが宿命というものかしら</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9040,29 +9040,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.earnest[1]</t>
+          <t xml:space="preserve">rivalry_70_up.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">繋いでもらったこの舞台、崩す気はないの。傷ごと、立つわ</t>
+          <t xml:space="preserve">戦えることに感謝してる。でも次は絶対に勝つわ</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9072,29 +9072,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.earnest[2]</t>
+          <t xml:space="preserve">trust_above_75.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来た以上、最後まできっちり向き合うわ。それが筋でしょ</t>
+          <t xml:space="preserve">この団体に貢献できるよう、これからも全力で努めるわ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9104,29 +9104,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.earnest[1]</t>
+          <t xml:space="preserve">trust_above_75.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手が誰でも、ちゃんと向き合うわ。手を抜くなんて、できないの</t>
+          <t xml:space="preserve">ここでプロレスができる幸せを噛みしめてるの</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9136,29 +9136,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.earnest[2]</t>
+          <t xml:space="preserve">trust_below_20.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">繋ぐ相手がいる。だから、この一戦も手は抜けないの</t>
+          <t xml:space="preserve">信じてたのに…もうここでは頑張れないかもしれないわ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9168,29 +9168,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.earnest[1]</t>
+          <t xml:space="preserve">trust_below_20.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒したわ。…でも、まだ役目の途中なの。次、出してよ。ちゃんと相手するから</t>
+          <t xml:space="preserve">全力を尽くしてきたつもりよ。でも、もう…</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9200,29 +9200,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.earnest[2]</t>
+          <t xml:space="preserve">trust_below_35.earnest.seductive[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの。繋ぐまでは、退けない。次の子、来なさい</t>
+          <t xml:space="preserve">この団体の方針に…少し不安を感じてるの</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9232,29 +9232,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.earnest[1]</t>
+          <t xml:space="preserve">trust_below_35.earnest.seductive[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で紡いだ勝利よ。この結び目を、一人でほどく気はないわ</t>
+          <t xml:space="preserve">自分の居場所がここにあるのか…考えてしまうわ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.earnest[2]</t>
+          <t xml:space="preserve">preFinal.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9279,14 +9279,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が信じてくれた……その信頼に、ちゃんと応えられたかしら</t>
+          <t xml:space="preserve">繋いでもらったこの舞台、崩す気はないの。傷ごと、立つわ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9296,12 +9296,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.earnest[1]</t>
+          <t xml:space="preserve">preFinal.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9311,14 +9311,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞は嬉しいわ。でも……本当に欲しかったのは、三人で掴む勝利</t>
+          <t xml:space="preserve">ここまで来た以上、最後まできっちり向き合うわ。それが筋でしょ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.earnest[2]</t>
+          <t xml:space="preserve">preMatch.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9343,14 +9343,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった分は、次に全て返す。約束するわ</t>
+          <t xml:space="preserve">相手が誰でも、ちゃんと向き合うわ。手を抜くなんて、できないの</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.earnest[1]</t>
+          <t xml:space="preserve">preMatch.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9375,14 +9375,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人一人、ちゃんと向き合ったわ。この身体で返した答えよ</t>
+          <t xml:space="preserve">繋ぐ相手がいる。だから、この一戦も手は抜けないの</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.earnest[2]</t>
+          <t xml:space="preserve">survivor.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9407,14 +9407,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界なんて何度も見えた。でも……ここで崩れるのは、許せなかったの</t>
+          <t xml:space="preserve">一人、倒したわ。…でも、まだ役目の途中なの。次、出してよ。ちゃんと相手するから</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">survivor.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9439,14 +9439,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でいくわ。最高の試合にしましょう</t>
+          <t xml:space="preserve">まだ立ってるの。繋ぐまでは、退けない。次の子、来なさい</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9471,14 +9471,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られたのは、支えてくれた皆のおかげよ。…ありがとう</t>
+          <t xml:space="preserve">三人で紡いだ勝利よ。この結び目を、一人でほどく気はないわ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9488,12 +9488,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">champion.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9503,14 +9503,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体のために戦えて…嬉しいわ</t>
+          <t xml:space="preserve">仲間が信じてくれた……その信頼に、ちゃんと応えられたかしら</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9520,29 +9520,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.earnest[1]</t>
+          <t xml:space="preserve">defiant.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきた全部が報われた…泣きそうだわ</t>
+          <t xml:space="preserve">賞は嬉しいわ。でも……本当に欲しかったのは、三人で掴む勝利</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9552,59 +9552,283 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">defiant.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてくれた人は久しぶりなの。…このチャンス、大事にするわ</t>
+          <t xml:space="preserve">足りなかった分は、次に全て返す。約束するわ</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人一人、ちゃんと向き合ったわ。この身体で返した答えよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.earnest[2]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.seductive.earnest[2]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">限界なんて何度も見えた。でも……ここで崩れるのは、許せなかったの</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力でいくわ。最高の試合にしましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来られたのは、支えてくれた皆のおかげよ。…ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体のために戦えて…嬉しいわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">積み重ねてきた全部が報われた…泣きそうだわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてくれた人は久しぶりなの。…このチャンス、大事にするわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.earnest[1]</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr" s="2">
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr" s="12">
+      <c r="D296" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr" s="2">
+      <c r="E296" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr" s="3">
+      <c r="F296" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">評価してくれたのね。…ちゃんと応えるわ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H289"/>
+  <autoFilter ref="A1:H296"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×真面目.xlsx
@@ -328,7 +328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H289"/>
+  <dimension ref="A1:H293"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -9030,7 +9030,7 @@
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9040,29 +9040,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.earnest[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">繋いでもらったこの舞台、崩す気はないの。傷ごと、立つわ</t>
+          <t xml:space="preserve">ふ……貴女、強いのね……</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9072,29 +9072,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.seductive.earnest[2]</t>
+          <t xml:space="preserve">GL-01.greatWin.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来た以上、最後まできっちり向き合うわ。それが筋でしょ</t>
+          <t xml:space="preserve">……夢を、見ているみたい……ですわね</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.earnest[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9104,29 +9104,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.earnest[1]</t>
+          <t xml:space="preserve">GL-01.loss.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手が誰でも、ちゃんと向き合うわ。手を抜くなんて、できないの</t>
+          <t xml:space="preserve">……まだ、わたし、足りませんわね……</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.earnest[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9136,29 +9136,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.seductive.earnest[2]</t>
+          <t xml:space="preserve">GL-01.win.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">繋ぐ相手がいる。だから、この一戦も手は抜けないの</t>
+          <t xml:space="preserve">ふふ……ここまで、こられたのですね</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9173,7 +9173,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.earnest[1]</t>
+          <t xml:space="preserve">preFinal.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9183,14 +9183,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒したわ。…でも、まだ役目の途中なの。次、出してよ。ちゃんと相手するから</t>
+          <t xml:space="preserve">繋いでもらったこの舞台、崩す気はないの。傷ごと、立つわ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.seductive.earnest[2]</t>
+          <t xml:space="preserve">preFinal.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9215,14 +9215,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってるの。繋ぐまでは、退けない。次の子、来なさい</t>
+          <t xml:space="preserve">ここまで来た以上、最後まできっちり向き合うわ。それが筋でしょ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.earnest[1]</t>
+          <t xml:space="preserve">preMatch.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9247,14 +9247,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で紡いだ勝利よ。この結び目を、一人でほどく気はないわ</t>
+          <t xml:space="preserve">相手が誰でも、ちゃんと向き合うわ。手を抜くなんて、できないの</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.seductive.earnest[2]</t>
+          <t xml:space="preserve">preMatch.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9279,14 +9279,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が信じてくれた……その信頼に、ちゃんと応えられたかしら</t>
+          <t xml:space="preserve">繋ぐ相手がいる。だから、この一戦も手は抜けないの</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9296,12 +9296,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.earnest[1]</t>
+          <t xml:space="preserve">survivor.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9311,14 +9311,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞は嬉しいわ。でも……本当に欲しかったのは、三人で掴む勝利</t>
+          <t xml:space="preserve">一人、倒したわ。…でも、まだ役目の途中なの。次、出してよ。ちゃんと相手するから</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.seductive.earnest[2]</t>
+          <t xml:space="preserve">survivor.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9343,14 +9343,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった分は、次に全て返す。約束するわ</t>
+          <t xml:space="preserve">まだ立ってるの。繋ぐまでは、退けない。次の子、来なさい</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.earnest[1]</t>
+          <t xml:space="preserve">champion.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9375,14 +9375,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人一人、ちゃんと向き合ったわ。この身体で返した答えよ</t>
+          <t xml:space="preserve">三人で紡いだ勝利よ。この結び目を、一人でほどく気はないわ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.earnest[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.seductive.earnest[2]</t>
+          <t xml:space="preserve">champion.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9407,14 +9407,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界なんて何度も見えた。でも……ここで崩れるのは、許せなかったの</t>
+          <t xml:space="preserve">仲間が信じてくれた……その信頼に、ちゃんと応えられたかしら</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">defiant.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9439,14 +9439,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でいくわ。最高の試合にしましょう</t>
+          <t xml:space="preserve">賞は嬉しいわ。でも……本当に欲しかったのは、三人で掴む勝利</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">defiant.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9471,14 +9471,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られたのは、支えてくれた皆のおかげよ。…ありがとう</t>
+          <t xml:space="preserve">足りなかった分は、次に全て返す。約束するわ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9488,12 +9488,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">seductive.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9503,14 +9503,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体のために戦えて…嬉しいわ</t>
+          <t xml:space="preserve">一人一人、ちゃんと向き合ったわ。この身体で返した答えよ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.seductive.earnest[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9520,29 +9520,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.seductive.earnest[1]</t>
+          <t xml:space="preserve">gauntlet.seductive.earnest[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきた全部が報われた…泣きそうだわ</t>
+          <t xml:space="preserve">限界なんて何度も見えた。でも……ここで崩れるのは、許せなかったの</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.seductive.earnest[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.seductive.earnest[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
@@ -9562,49 +9562,177 @@
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてくれた人は久しぶりなの。…このチャンス、大事にするわ</t>
+          <t xml:space="preserve">全力でいくわ。最高の試合にしましょう</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来られたのは、支えてくれた皆のおかげよ。…ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">団体のために戦えて…嬉しいわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">積み重ねてきた全部が報われた…泣きそうだわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">seductive.earnest[1]</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてくれた人は久しぶりなの。…このチャンス、大事にするわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.seductive.earnest[1]</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr" s="2">
+      <c r="B293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr" s="12">
+      <c r="D293" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">seductive.earnest[1]</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr" s="2">
+      <c r="E293" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr" s="3">
+      <c r="F293" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">評価してくれたのね。…ちゃんと応えるわ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H289"/>
+  <autoFilter ref="A1:H293"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/蠱惑×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×真面目.xlsx
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あの人とやらせてほしいの。お願いします。</t>
+          <t xml:space="preserve">社長、三人であちらへ行かせてほしいの。お願いします。</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしてもあの人とやりたくて。……聞いてくれる？</t>
+          <t xml:space="preserve">どうしても三人で乗り込みたくて。……聞いてくれる？</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身勝手なお願いなの。あの人と、やらせて。</t>
+          <t xml:space="preserve">身勝手なお願いなの。三人で、あちらへ行かせて。</t>
         </is>
       </c>
     </row>

--- a/セリフ編集/キャラタイプ別/蠱惑×真面目.xlsx
+++ b/セリフ編集/キャラタイプ別/蠱惑×真面目.xlsx
@@ -9343,7 +9343,7 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ、わたし、足りませんわね……</t>
+          <t xml:space="preserve">……敗因は、分かっているの。次は、同じようにはいかないわ</t>
         </is>
       </c>
     </row>
